--- a/internacional/2_8/Contraste_tierra_espacio.xlsx
+++ b/internacional/2_8/Contraste_tierra_espacio.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE77"/>
+  <dimension ref="A1:AH79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -587,6 +587,21 @@
           <t>TW esp</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Grado SV solido</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura amplia</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura estricta</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -606,7 +621,7 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
@@ -635,6 +650,19 @@
       <c r="V2" t="n">
         <v>1</v>
       </c>
+      <c r="AF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -654,7 +682,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -695,11 +723,27 @@
       <c r="V3" t="n">
         <v>1</v>
       </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -708,19 +752,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="K4" t="n">
-        <v>8</v>
+      <c r="M4" t="n">
+        <v>7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -728,14 +784,27 @@
       <c r="S4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="n">
-        <v>1</v>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Capas de la atmósfera y variación con la altitud</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -744,34 +813,86 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
       </c>
       <c r="J5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K5" t="n">
         <v>7</v>
       </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
       <c r="V5" t="n">
         <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Capas internas de la Tierra</t>
+          <t>Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -780,30 +901,27 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>7</v>
       </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
       <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
@@ -812,14 +930,30 @@
       <c r="S6" t="n">
         <v>1</v>
       </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
       <c r="V6" t="n">
         <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>El Sol como estrella</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,39 +967,24 @@
       <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="L7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
@@ -881,17 +1000,27 @@
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
       <c r="V7" t="n">
         <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Fósiles y su formación</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,28 +1029,71 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Eclipses solares y lunares</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -930,46 +1102,80 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
         <v>6</v>
       </c>
       <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
       <c r="V9" t="n">
         <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Sol como estrella</t>
+          <t>Galaxias y escala del universo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -978,10 +1184,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
@@ -989,14 +1195,11 @@
       <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
         <v>7</v>
@@ -1007,9 +1210,6 @@
       <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
@@ -1018,12 +1218,25 @@
       </c>
       <c r="V10" t="n">
         <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1032,22 +1245,71 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>Límites de placas: convergentes, divergentes y transformantes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1056,22 +1318,53 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="T12" t="n">
-        <v>1</v>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fósiles y su formación</t>
+          <t>Origen del magma y vulcanismo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1080,37 +1373,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1121,17 +1399,27 @@
       <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
       <c r="V13" t="n">
         <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1140,34 +1428,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1178,12 +1460,6 @@
       <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
@@ -1192,12 +1468,25 @@
       </c>
       <c r="V14" t="n">
         <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo</t>
+          <t>El océano: propiedades del agua de mar y zonas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1206,27 +1495,24 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
         <v>7</v>
       </c>
-      <c r="P15" t="n">
+      <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
@@ -1235,17 +1521,27 @@
       <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
       <c r="V15" t="n">
         <v>1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Impacto de las actividades humanas en los recursos</t>
+          <t>Registro fósil y cambios ambientales del pasado</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1254,34 +1550,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>7</v>
-      </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -1295,17 +1582,27 @@
       <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
       <c r="V16" t="n">
         <v>1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Límites de placas: convergentes, divergentes y transformantes</t>
+          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1314,40 +1611,62 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Sismos y fallas geológicas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1356,40 +1675,59 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
       </c>
       <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
         <v>5</v>
       </c>
       <c r="J18" t="n">
         <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
-      </c>
-      <c r="N18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="V18" t="n">
         <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Origen del magma y vulcanismo</t>
+          <t>Tectónica de placas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1403,17 +1741,38 @@
       <c r="D19" t="n">
         <v>4</v>
       </c>
+      <c r="E19" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>7</v>
       </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1424,14 +1783,30 @@
       <c r="S19" t="n">
         <v>1</v>
       </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
       <c r="V19" t="n">
         <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1440,30 +1815,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
       </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" t="n">
         <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>7</v>
-      </c>
-      <c r="O20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="n">
@@ -1472,20 +1850,36 @@
       <c r="Q20" t="n">
         <v>1</v>
       </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
       <c r="V20" t="n">
         <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>El océano: propiedades del agua de mar y zonas</t>
+          <t>Volcanes: estructura, tipos y productos</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1500,113 +1894,160 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
       </c>
       <c r="J21" t="n">
         <v>2.5</v>
       </c>
-      <c r="M21" t="n">
-        <v>7</v>
-      </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="V21" t="n">
-        <v>1</v>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registro fósil y cambios ambientales del pasado</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K22" t="n">
         <v>6</v>
       </c>
-      <c r="J22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3</v>
+      <c r="L22" t="n">
+        <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
       <c r="V22" t="n">
         <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
@@ -1616,77 +2057,115 @@
       <c r="S23" t="n">
         <v>1</v>
       </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
       <c r="V23" t="n">
         <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sismos y fallas geológicas</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
       <c r="H24" t="n">
-        <v>5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>2.5</v>
       </c>
+      <c r="K24" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M24" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
       <c r="V24" t="n">
         <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sistemas terrestres y sus interacciones</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
@@ -1695,22 +2174,13 @@
         <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -1721,65 +2191,60 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="n">
         <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tectónica de placas</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>6</v>
       </c>
       <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K26" t="n">
         <v>4</v>
       </c>
-      <c r="I26" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>7</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3</v>
-      </c>
       <c r="M26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -1787,9 +2252,6 @@
       <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
@@ -1798,43 +2260,65 @@
       </c>
       <c r="V26" t="n">
         <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
@@ -1844,50 +2328,60 @@
       <c r="S27" t="n">
         <v>1</v>
       </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
       <c r="V27" t="n">
         <v>1</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
         <v>5</v>
       </c>
+      <c r="L28" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -1895,59 +2389,115 @@
       <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
       <c r="V28" t="n">
         <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Volcanes: estructura, tipos y productos</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>2.5</v>
       </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
       <c r="R29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Acidificación del océano</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1956,22 +2506,59 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
+      <c r="M30" t="n">
         <v>7</v>
       </c>
-      <c r="D30" t="n">
-        <v>7</v>
-      </c>
-      <c r="H30" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1980,58 +2567,53 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
         <v>7</v>
       </c>
-      <c r="D31" t="n">
-        <v>7</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K31" t="n">
-        <v>6</v>
-      </c>
-      <c r="L31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>7</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
+      <c r="AF31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2040,34 +2622,71 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
-      </c>
-      <c r="F32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K32" t="n">
         <v>8</v>
       </c>
-      <c r="H32" t="n">
-        <v>7</v>
-      </c>
       <c r="M32" t="n">
-        <v>7</v>
-      </c>
-      <c r="O32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
         <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
       <c r="V32" t="n">
         <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2076,41 +2695,26 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
         <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M33" t="n">
         <v>4.5</v>
       </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
@@ -2123,17 +2727,27 @@
       <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
       <c r="V33" t="n">
         <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2148,22 +2762,16 @@
         <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
-      </c>
-      <c r="G34" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M34" t="n">
         <v>4.5</v>
@@ -2171,10 +2779,7 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="n">
@@ -2183,17 +2788,27 @@
       <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
       <c r="V34" t="n">
         <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ciclo de las rocas</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2202,52 +2817,59 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
         <v>4</v>
       </c>
-      <c r="I35" t="n">
-        <v>5</v>
-      </c>
-      <c r="J35" t="n">
-        <v>7</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2256,31 +2878,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" t="n">
-        <v>6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>5</v>
-      </c>
       <c r="J36" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
-      </c>
-      <c r="L36" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
         <v>2.5</v>
@@ -2294,7 +2913,7 @@
       <c r="P36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="n">
@@ -2303,17 +2922,27 @@
       <c r="T36" t="n">
         <v>1</v>
       </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
       <c r="V36" t="n">
         <v>1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2322,22 +2951,65 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
       </c>
       <c r="M37" t="n">
         <v>4.5</v>
       </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
       <c r="V37" t="n">
         <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2346,46 +3018,68 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
-      </c>
-      <c r="G38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
         <v>4</v>
       </c>
+      <c r="J38" t="n">
+        <v>4.5</v>
+      </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="P38" t="n">
-        <v>1</v>
-      </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" t="n">
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="n">
         <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2394,25 +3088,37 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.5</v>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
       <c r="J39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M39" t="n">
         <v>2.5</v>
       </c>
-      <c r="K39" t="n">
-        <v>4</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4.5</v>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -2420,20 +3126,33 @@
       <c r="Q39" t="n">
         <v>1</v>
       </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
       <c r="V39" t="n">
         <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2442,28 +3161,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F40" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H40" t="n">
         <v>4</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K40" t="n">
         <v>6</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>8</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
       </c>
       <c r="M40" t="n">
         <v>2.5</v>
@@ -2489,11 +3208,27 @@
       <c r="V40" t="n">
         <v>1</v>
       </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2502,52 +3237,71 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
       </c>
       <c r="H41" t="n">
         <v>2</v>
       </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K41" t="n">
-        <v>7</v>
-      </c>
-      <c r="L41" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M41" t="n">
         <v>2.5</v>
       </c>
-      <c r="O41" t="n">
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
       <c r="V41" t="n">
         <v>1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2556,32 +3310,44 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
         <v>2.5</v>
       </c>
       <c r="K42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
         <v>4.5</v>
       </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
@@ -2596,12 +3362,25 @@
       </c>
       <c r="V42" t="n">
         <v>1</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2610,28 +3389,34 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K43" t="n">
         <v>7</v>
       </c>
-      <c r="D43" t="n">
-        <v>7</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6</v>
-      </c>
-      <c r="H43" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" t="n">
-        <v>5</v>
-      </c>
-      <c r="L43" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -2639,23 +3424,36 @@
       <c r="Q43" t="n">
         <v>1</v>
       </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
       <c r="V43" t="n">
         <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2664,31 +3462,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
         <v>2.5</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
         <v>2.5</v>
@@ -2717,212 +3515,241 @@
       <c r="V44" t="n">
         <v>1</v>
       </c>
+      <c r="AF44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Acidificación del océano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
-      </c>
-      <c r="G45" t="n">
-        <v>6</v>
-      </c>
-      <c r="I45" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K45" t="n">
-        <v>5</v>
-      </c>
-      <c r="M45" t="n">
         <v>7</v>
       </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1</v>
+      <c r="H45" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
-      </c>
-      <c r="I46" t="n">
         <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
       <c r="S46" t="n">
         <v>1</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" t="n">
+        <v>7</v>
+      </c>
+      <c r="M47" t="n">
+        <v>7</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C47" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>3</v>
-      </c>
-      <c r="J47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K47" t="n">
-        <v>8</v>
-      </c>
-      <c r="M47" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geología y geomorfología de El Salvador</t>
+          <t>Capas de la atmósfera y variación con la altitud</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
-      </c>
-      <c r="F48" t="n">
-        <v>4</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Ciclo de las rocas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
         <v>4</v>
       </c>
-      <c r="D49" t="n">
+      <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="n">
         <v>4</v>
       </c>
-      <c r="G49" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2</v>
-      </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>7</v>
       </c>
-      <c r="M49" t="n">
-        <v>4.5</v>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -2936,155 +3763,200 @@
       <c r="S49" t="n">
         <v>1</v>
       </c>
-      <c r="V49" t="n">
-        <v>1</v>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4</v>
+      </c>
+      <c r="L50" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
         <v>2</v>
       </c>
-      <c r="I51" t="n">
-        <v>8</v>
-      </c>
       <c r="J51" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="L51" t="n">
+        <v>5</v>
       </c>
       <c r="M51" t="n">
         <v>2.5</v>
       </c>
-      <c r="N51" t="n">
-        <v>1</v>
-      </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
       <c r="S51" t="n">
         <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
       <c r="V51" t="n">
         <v>1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H52" t="n">
         <v>7</v>
       </c>
-      <c r="D52" t="n">
-        <v>7</v>
-      </c>
-      <c r="F52" t="n">
-        <v>4</v>
-      </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K52" t="n">
         <v>7</v>
@@ -3095,6 +3967,9 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
@@ -3106,147 +3981,108 @@
       </c>
       <c r="V52" t="n">
         <v>1</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Energía geotérmica</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="G53" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>7</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>no_aplica</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
-      </c>
-      <c r="E54" t="n">
-        <v>4</v>
-      </c>
-      <c r="F54" t="n">
-        <v>4</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" t="n">
-        <v>7</v>
-      </c>
-      <c r="K54" t="n">
-        <v>3</v>
-      </c>
-      <c r="M54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>no_aplica</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5</v>
       </c>
       <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K55" t="n">
         <v>7</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3</v>
       </c>
       <c r="M55" t="n">
         <v>4.5</v>
@@ -3254,7 +4090,7 @@
       <c r="N55" t="n">
         <v>1</v>
       </c>
-      <c r="P55" t="n">
+      <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="Q55" t="n">
@@ -3268,40 +4104,59 @@
       </c>
       <c r="V55" t="n">
         <v>1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>2.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
       </c>
       <c r="H56" t="n">
         <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J56" t="n">
         <v>4.5</v>
       </c>
+      <c r="K56" t="n">
+        <v>8</v>
+      </c>
       <c r="M56" t="n">
         <v>2.5</v>
       </c>
@@ -3311,6 +4166,9 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
@@ -3320,19 +4178,35 @@
       <c r="S56" t="n">
         <v>1</v>
       </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
       <c r="V56" t="n">
         <v>1</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oleaje, dinámica costera y sedimentación marina</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3341,141 +4215,186 @@
       <c r="D57" t="n">
         <v>4</v>
       </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="H57" t="n">
+        <v>5</v>
+      </c>
       <c r="J57" t="n">
         <v>2.5</v>
       </c>
       <c r="M57" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
       </c>
       <c r="V57" t="n">
         <v>1</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad</t>
+          <t>Oleaje, dinámica costera y sedimentación marina</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>6</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>8</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" t="n">
-        <v>2</v>
-      </c>
-      <c r="F59" t="n">
-        <v>4</v>
-      </c>
-      <c r="G59" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" t="n">
-        <v>2</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M59" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>5</v>
       </c>
       <c r="H60" t="n">
-        <v>4</v>
-      </c>
-      <c r="I60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M60" t="n">
         <v>4.5</v>
       </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
       <c r="S60" t="n">
         <v>1</v>
       </c>
@@ -3484,46 +4403,65 @@
       </c>
       <c r="V60" t="n">
         <v>1</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>Recursos naturales renovables y no renovables</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
-      </c>
-      <c r="I61" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>4.5</v>
       </c>
       <c r="K61" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="L61" t="n">
+        <v>5</v>
       </c>
       <c r="M61" t="n">
         <v>2.5</v>
       </c>
+      <c r="N61" t="n">
+        <v>1</v>
+      </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
@@ -3533,53 +4471,60 @@
       <c r="Q61" t="n">
         <v>1</v>
       </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
       <c r="S61" t="n">
         <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
+      <c r="U61" t="n">
+        <v>1</v>
+      </c>
       <c r="V61" t="n">
         <v>1</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
-      </c>
-      <c r="F62" t="n">
         <v>4</v>
       </c>
       <c r="H62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>3</v>
-      </c>
-      <c r="M62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
@@ -3590,51 +4535,67 @@
       <c r="T62" t="n">
         <v>1</v>
       </c>
-      <c r="V62" t="n">
-        <v>1</v>
+      <c r="AF62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Sistemas terrestres y sus interacciones</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H63" t="n">
         <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
         <v>1</v>
       </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
       <c r="P63" t="n">
         <v>1</v>
       </c>
@@ -3652,53 +4613,91 @@
       </c>
       <c r="V63" t="n">
         <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>6</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3</v>
+      </c>
+      <c r="M64" t="n">
+        <v>7</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C64" t="n">
-        <v>4</v>
-      </c>
-      <c r="D64" t="n">
-        <v>4</v>
-      </c>
-      <c r="H64" t="n">
-        <v>5</v>
-      </c>
-      <c r="J64" t="n">
-        <v>7</v>
-      </c>
-      <c r="K64" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="T64" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3707,238 +4706,188 @@
       <c r="D65" t="n">
         <v>4</v>
       </c>
-      <c r="E65" t="n">
-        <v>2</v>
-      </c>
       <c r="F65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" t="n">
+        <v>7</v>
+      </c>
+      <c r="J65" t="n">
+        <v>7</v>
+      </c>
+      <c r="M65" t="n">
+        <v>7</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
         <v>4</v>
       </c>
-      <c r="G65" t="n">
-        <v>3</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2</v>
-      </c>
-      <c r="I65" t="n">
-        <v>8</v>
-      </c>
-      <c r="J65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K65" t="n">
-        <v>5</v>
-      </c>
-      <c r="M65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1</v>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Tsunamis</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
-      </c>
-      <c r="F66" t="n">
         <v>4</v>
       </c>
-      <c r="G66" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" t="n">
+      <c r="M66" t="n">
         <v>4.5</v>
       </c>
-      <c r="K66" t="n">
-        <v>7</v>
-      </c>
-      <c r="M66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1</v>
-      </c>
-      <c r="T66" t="n">
-        <v>1</v>
-      </c>
       <c r="V66" t="n">
         <v>1</v>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>no_aplica</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Uso del suelo y su degradación</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
           <t>alineado</t>
         </is>
-      </c>
-      <c r="C67" t="n">
-        <v>5</v>
-      </c>
-      <c r="D67" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" t="n">
-        <v>7</v>
-      </c>
-      <c r="H67" t="n">
-        <v>4</v>
-      </c>
-      <c r="I67" t="n">
-        <v>6</v>
-      </c>
-      <c r="K67" t="n">
-        <v>3</v>
-      </c>
-      <c r="M67" t="n">
-        <v>7</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
+          <t>Corrientes oceánicas superficiales y profundas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" t="n">
-        <v>3</v>
-      </c>
-      <c r="E68" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F68" t="n">
         <v>8</v>
       </c>
-      <c r="G68" t="n">
-        <v>2</v>
-      </c>
-      <c r="H68" t="n">
-        <v>3</v>
-      </c>
-      <c r="I68" t="n">
-        <v>5</v>
-      </c>
       <c r="J68" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K68" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M68" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N68" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="P68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
       <c r="S68" t="n">
         <v>1</v>
       </c>
-      <c r="T68" t="n">
-        <v>1</v>
-      </c>
       <c r="V68" t="n">
         <v>1</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>posterior</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tsunamis</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3953,16 +4902,29 @@
       <c r="V69" t="n">
         <v>1</v>
       </c>
+      <c r="AF69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Uso del suelo y su degradación</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3971,62 +4933,67 @@
       <c r="D70" t="n">
         <v>5</v>
       </c>
-      <c r="F70" t="n">
-        <v>4</v>
-      </c>
-      <c r="K70" t="n">
-        <v>2</v>
-      </c>
-      <c r="M70" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1</v>
+      <c r="E70" t="n">
+        <v>7</v>
+      </c>
+      <c r="J70" t="n">
+        <v>7</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Corrientes oceánicas superficiales y profundas</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
-      </c>
-      <c r="F71" t="n">
-        <v>8</v>
-      </c>
-      <c r="J71" t="n">
-        <v>7</v>
-      </c>
-      <c r="M71" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1</v>
-      </c>
-      <c r="S71" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4035,16 +5002,35 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4058,11 +5044,30 @@
       <c r="D73" t="n">
         <v>4</v>
       </c>
+      <c r="K73" t="n">
+        <v>8</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sismicidad de El Salvador</t>
+          <t>Geología y geomorfología de El Salvador</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4071,16 +5076,35 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vulcanismo de El Salvador</t>
+          <t>Ondas sísmicas, magnitud e intensidad</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4089,142 +5113,201 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Recursos naturales renovables y no renovables</t>
+          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
-      </c>
-      <c r="E76" t="n">
-        <v>2</v>
-      </c>
-      <c r="F76" t="n">
         <v>4</v>
       </c>
-      <c r="G76" t="n">
-        <v>6</v>
-      </c>
-      <c r="H76" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K76" t="n">
-        <v>4</v>
-      </c>
-      <c r="L76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M76" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="P76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
-        <v>1</v>
-      </c>
-      <c r="T76" t="n">
-        <v>1</v>
-      </c>
-      <c r="U76" t="n">
-        <v>1</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1</v>
+      <c r="AF76" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Sismicidad de El Salvador</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Vulcanismo de El Salvador</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4</v>
+      </c>
+      <c r="D78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>sin_referente</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>Suelo: formación, componentes y tipos</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>tardio</t>
         </is>
       </c>
-      <c r="C77" t="n">
-        <v>5</v>
-      </c>
-      <c r="D77" t="n">
-        <v>5</v>
-      </c>
-      <c r="E77" t="n">
-        <v>2</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2</v>
-      </c>
-      <c r="H77" t="n">
-        <v>3</v>
-      </c>
-      <c r="I77" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" t="n">
+      <c r="C79" t="n">
+        <v>5</v>
+      </c>
+      <c r="D79" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" t="n">
         <v>7</v>
       </c>
-      <c r="K77" t="n">
-        <v>2</v>
-      </c>
-      <c r="M77" t="n">
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
+      <c r="M79" t="n">
         <v>2.5</v>
       </c>
-      <c r="N77" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>1</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
-      <c r="S77" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" t="n">
-        <v>1</v>
-      </c>
-      <c r="V77" t="n">
-        <v>1</v>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4238,7 +5321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7485,6 +8568,90 @@
       </c>
       <c r="J77">
         <f>Datos!B77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <f>Datos!A78</f>
+        <v/>
+      </c>
+      <c r="B78">
+        <f>IF(Datos!C78="","",Datos!C78)</f>
+        <v/>
+      </c>
+      <c r="C78">
+        <f>COUNT(Datos!E78:M78)</f>
+        <v/>
+      </c>
+      <c r="D78">
+        <f>IF(C78=0,"",MEDIAN(Datos!E78:M78))</f>
+        <v/>
+      </c>
+      <c r="E78">
+        <f>COUNT(Datos!W78:AE78)</f>
+        <v/>
+      </c>
+      <c r="F78">
+        <f>IF(OR(B78="",D78=""),"",B78-D78)</f>
+        <v/>
+      </c>
+      <c r="G78">
+        <f>IF(Datos!D78="","",Datos!D78)</f>
+        <v/>
+      </c>
+      <c r="H78">
+        <f>COUNT(Datos!N78:V78)</f>
+        <v/>
+      </c>
+      <c r="I78">
+        <f>IF(B78="",IF(C78&gt;=5,"falta en SV",""),IF(G78="",IF(B78&gt;8,IF(C78&gt;=5,"SV tarde","despues del tramo"),IF(H78&gt;=5,"no retomado en 2-8","previo")),IF(B78&lt;2,"retomado",IF(AND(C78&lt;=1,E78&gt;=3),"solo especializacion",IF(F78="","coherente",IF(F78&lt;=-1.5,"SV adelantado",IF(F78&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J78">
+        <f>Datos!B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <f>Datos!A79</f>
+        <v/>
+      </c>
+      <c r="B79">
+        <f>IF(Datos!C79="","",Datos!C79)</f>
+        <v/>
+      </c>
+      <c r="C79">
+        <f>COUNT(Datos!E79:M79)</f>
+        <v/>
+      </c>
+      <c r="D79">
+        <f>IF(C79=0,"",MEDIAN(Datos!E79:M79))</f>
+        <v/>
+      </c>
+      <c r="E79">
+        <f>COUNT(Datos!W79:AE79)</f>
+        <v/>
+      </c>
+      <c r="F79">
+        <f>IF(OR(B79="",D79=""),"",B79-D79)</f>
+        <v/>
+      </c>
+      <c r="G79">
+        <f>IF(Datos!D79="","",Datos!D79)</f>
+        <v/>
+      </c>
+      <c r="H79">
+        <f>COUNT(Datos!N79:V79)</f>
+        <v/>
+      </c>
+      <c r="I79">
+        <f>IF(B79="",IF(C79&gt;=5,"falta en SV",""),IF(G79="",IF(B79&gt;8,IF(C79&gt;=5,"SV tarde","despues del tramo"),IF(H79&gt;=5,"no retomado en 2-8","previo")),IF(B79&lt;2,"retomado",IF(AND(C79&lt;=1,E79&gt;=3),"solo especializacion",IF(F79="","coherente",IF(F79&lt;=-1.5,"SV adelantado",IF(F79&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J79">
+        <f>Datos!B79</f>
         <v/>
       </c>
     </row>
@@ -7499,7 +8666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -7524,7 +8691,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Datos!B2:B77,A2)</f>
+        <f>COUNTIF(Datos!B2:B79,A2)</f>
         <v/>
       </c>
     </row>
@@ -7535,7 +8702,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Datos!B2:B77,A3)</f>
+        <f>COUNTIF(Datos!B2:B79,A3)</f>
         <v/>
       </c>
     </row>
@@ -7546,7 +8713,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Datos!B2:B77,A4)</f>
+        <f>COUNTIF(Datos!B2:B79,A4)</f>
         <v/>
       </c>
     </row>
@@ -7557,7 +8724,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Datos!B2:B77,A5)</f>
+        <f>COUNTIF(Datos!B2:B79,A5)</f>
         <v/>
       </c>
     </row>
@@ -7568,7 +8735,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Datos!B2:B77,A6)</f>
+        <f>COUNTIF(Datos!B2:B79,A6)</f>
         <v/>
       </c>
     </row>
@@ -7579,18 +8746,29 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Datos!B2:B77,A7)</f>
+        <f>COUNTIF(Datos!B2:B79,A7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>incierto</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>COUNTIF(Datos!B2:B79,A8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8">
-        <f>SUM(B2:B7)</f>
+      <c r="B9">
+        <f>SUM(B2:B8)</f>
         <v/>
       </c>
     </row>

--- a/internacional/2_8/Contraste_tierra_espacio.xlsx
+++ b/internacional/2_8/Contraste_tierra_espacio.xlsx
@@ -804,7 +804,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Ciclo de las rocas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -813,44 +813,32 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
@@ -866,15 +854,6 @@
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
       <c r="AF5" t="n">
         <v>3</v>
       </c>
@@ -885,14 +864,14 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Eclipses solares y lunares</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -901,43 +880,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
       </c>
       <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
         <v>7</v>
       </c>
-      <c r="K6" t="n">
-        <v>8</v>
+      <c r="L6" t="n">
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -953,7 +959,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>El Sol como estrella</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -962,50 +968,53 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
         <v>2.5</v>
       </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
         <v>7</v>
       </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
           <t>adelantado</t>
@@ -1013,14 +1022,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fósiles y su formación</t>
+          <t>Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1029,55 +1038,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="M8" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
         <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>3</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1093,7 +1090,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>El Sol como estrella</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1106,33 +1103,24 @@
       </c>
       <c r="D9" t="n">
         <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1149,13 +1137,7 @@
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
       <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
@@ -1175,7 +1157,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo</t>
+          <t>Fósiles y su formación</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1184,25 +1166,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
       </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1210,6 +1201,9 @@
       <c r="Q10" t="n">
         <v>1</v>
       </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
@@ -1220,7 +1214,7 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1236,7 +1230,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Impacto de las actividades humanas en los recursos</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1253,20 +1247,23 @@
       <c r="F11" t="n">
         <v>5</v>
       </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
         <v>2.5</v>
@@ -1274,6 +1271,9 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
@@ -1290,6 +1290,9 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
@@ -1309,7 +1312,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Límites de placas: convergentes, divergentes y transformantes</t>
+          <t>Galaxias y escala del universo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1318,30 +1321,36 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
       </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
       <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="V12" t="n">
@@ -1364,7 +1373,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Origen del magma y vulcanismo</t>
+          <t>Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1373,22 +1382,34 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1399,11 +1420,17 @@
       <c r="S13" t="n">
         <v>1</v>
       </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
       <c r="V13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -1419,7 +1446,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>Límites de placas: convergentes, divergentes y transformantes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1428,49 +1455,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" t="n">
         <v>7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5</v>
       </c>
       <c r="M14" t="n">
         <v>7</v>
       </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="V14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -1486,7 +1501,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>El océano: propiedades del agua de mar y zonas</t>
+          <t>Origen del magma y vulcanismo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1495,29 +1510,29 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
         <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.5</v>
       </c>
       <c r="M15" t="n">
         <v>7</v>
       </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
@@ -1525,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -1541,7 +1556,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Registro fósil y cambios ambientales del pasado</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1555,31 +1570,37 @@
       <c r="D16" t="n">
         <v>3</v>
       </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.5</v>
+      </c>
       <c r="H16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
       <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
         <v>1</v>
       </c>
       <c r="V16" t="n">
@@ -1602,7 +1623,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
+          <t>El océano: propiedades del agua de mar y zonas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1611,25 +1632,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J17" t="n">
         <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1637,20 +1655,14 @@
       <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1</v>
-      </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -1666,7 +1678,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sismos y fallas geológicas</t>
+          <t>Registro fósil y cambios ambientales del pasado</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1675,28 +1687,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -1707,11 +1716,14 @@
       <c r="S18" t="n">
         <v>1</v>
       </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
       <c r="V18" t="n">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -1727,7 +1739,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tectónica de placas</t>
+          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1736,44 +1748,29 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
         <v>6</v>
       </c>
-      <c r="H19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" t="n">
-        <v>5</v>
-      </c>
       <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
         <v>2.5</v>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
@@ -1783,14 +1780,14 @@
       <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
       <c r="V19" t="n">
         <v>1</v>
       </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
       <c r="AF19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -1806,7 +1803,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Sismos y fallas geológicas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1820,31 +1817,22 @@
       <c r="D20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3</v>
+      <c r="F20" t="n">
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
@@ -1854,9 +1842,6 @@
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="n">
@@ -1879,7 +1864,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Volcanes: estructura, tipos y productos</t>
+          <t>Tectónica de placas</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1888,31 +1873,61 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
       <c r="I21" t="n">
         <v>5</v>
       </c>
       <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
         <v>2.5</v>
       </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -1928,42 +1943,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
         <v>8</v>
       </c>
-      <c r="G22" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
-      </c>
       <c r="J22" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
-      </c>
-      <c r="O22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="P22" t="n">
@@ -1972,115 +1987,85 @@
       <c r="Q22" t="n">
         <v>1</v>
       </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Volcanes: estructura, tipos y productos</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="n">
         <v>2.5</v>
       </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L23" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
       <c r="R23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
       <c r="AF23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2107,13 +2092,13 @@
         <v>2.5</v>
       </c>
       <c r="K24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>7.5</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2153,7 +2138,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2162,25 +2147,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2191,17 +2188,20 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1</v>
-      </c>
       <c r="AF25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2210,14 +2210,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2226,16 +2226,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
       </c>
       <c r="G26" t="n">
         <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>2.5</v>
@@ -2243,9 +2246,15 @@
       <c r="K26" t="n">
         <v>4</v>
       </c>
+      <c r="L26" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M26" t="n">
         <v>4.5</v>
       </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
@@ -2258,11 +2267,14 @@
       <c r="T26" t="n">
         <v>1</v>
       </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
       <c r="V26" t="n">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2278,7 +2290,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2287,10 +2299,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -2299,20 +2314,23 @@
         <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7.5</v>
       </c>
       <c r="M27" t="n">
         <v>2.5</v>
       </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
@@ -2322,24 +2340,24 @@
       <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
       <c r="V27" t="n">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -2351,7 +2369,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2365,40 +2383,37 @@
       <c r="D28" t="n">
         <v>7</v>
       </c>
+      <c r="F28" t="n">
+        <v>8</v>
+      </c>
       <c r="G28" t="n">
         <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
         <v>7</v>
       </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
       <c r="P28" t="n">
         <v>1</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
       <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
@@ -2418,7 +2433,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2427,40 +2442,25 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>2.5</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2468,9 +2468,6 @@
       <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
@@ -2481,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2497,7 +2494,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2506,29 +2503,41 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
       </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
         <v>2.5</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
       </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
@@ -2542,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -2558,7 +2567,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2567,16 +2576,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J31" t="n">
         <v>7</v>
@@ -2584,20 +2593,32 @@
       <c r="K31" t="n">
         <v>5</v>
       </c>
+      <c r="L31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
       <c r="AF31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2613,7 +2634,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2622,28 +2643,31 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
         <v>4</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" t="n">
         <v>4</v>
       </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>2.5</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
         <v>2.5</v>
@@ -2651,6 +2675,9 @@
       <c r="N32" t="n">
         <v>1</v>
       </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
@@ -2670,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -2686,7 +2713,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2695,43 +2722,43 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" t="n">
         <v>7</v>
       </c>
-      <c r="M33" t="n">
-        <v>4.5</v>
-      </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -2747,7 +2774,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2756,27 +2783,24 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>7</v>
-      </c>
-      <c r="M34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="R34" t="n">
@@ -2788,11 +2812,8 @@
       <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
       <c r="AF34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -2808,7 +2829,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2822,6 +2843,9 @@
       <c r="D35" t="n">
         <v>4</v>
       </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
       <c r="G35" t="n">
         <v>3</v>
       </c>
@@ -2829,13 +2853,19 @@
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>2.5</v>
       </c>
+      <c r="K35" t="n">
+        <v>8</v>
+      </c>
       <c r="M35" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2847,6 +2877,9 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="V35" t="n">
@@ -2869,7 +2902,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2878,55 +2911,43 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4</v>
-      </c>
-      <c r="F36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
         <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
       </c>
-      <c r="K36" t="n">
-        <v>3</v>
-      </c>
       <c r="M36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
       </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
       </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
       <c r="V36" t="n">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -2942,7 +2963,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2951,25 +2972,25 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5</v>
       </c>
       <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K37" t="n">
         <v>7</v>
-      </c>
-      <c r="J37" t="n">
-        <v>7</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
       </c>
       <c r="M37" t="n">
         <v>4.5</v>
@@ -2977,7 +2998,7 @@
       <c r="N37" t="n">
         <v>1</v>
       </c>
-      <c r="P37" t="n">
+      <c r="O37" t="n">
         <v>1</v>
       </c>
       <c r="Q37" t="n">
@@ -2993,11 +3014,11 @@
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -3009,7 +3030,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3018,26 +3039,32 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J38" t="n">
         <v>4.5</v>
       </c>
+      <c r="K38" t="n">
+        <v>8</v>
+      </c>
       <c r="M38" t="n">
         <v>2.5</v>
       </c>
@@ -3047,6 +3074,9 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
@@ -3056,10 +3086,10 @@
       <c r="S38" t="n">
         <v>1</v>
       </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
       <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
         <v>1</v>
       </c>
       <c r="AF38" t="n">
@@ -3067,7 +3097,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -3079,7 +3109,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3088,55 +3118,43 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7</v>
+      </c>
+      <c r="M39" t="n">
         <v>4.5</v>
       </c>
-      <c r="M39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3152,7 +3170,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3161,58 +3179,43 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
-      </c>
-      <c r="F40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>7</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
         <v>4</v>
-      </c>
-      <c r="I40" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>6</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>8</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3228,7 +3231,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3237,28 +3240,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" t="n">
         <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
         <v>2.5</v>
@@ -3266,12 +3269,12 @@
       <c r="N41" t="n">
         <v>1</v>
       </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
@@ -3285,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -3301,7 +3304,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3310,31 +3313,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
       </c>
-      <c r="F42" t="n">
-        <v>5</v>
-      </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
         <v>4.5</v>
@@ -3342,18 +3339,12 @@
       <c r="N42" t="n">
         <v>1</v>
       </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
@@ -3364,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3380,7 +3371,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3389,38 +3380,35 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>4.5</v>
       </c>
-      <c r="K43" t="n">
-        <v>7</v>
-      </c>
       <c r="M43" t="n">
         <v>2.5</v>
       </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
@@ -3430,14 +3418,14 @@
       <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
+      <c r="Z43" t="n">
+        <v>1</v>
+      </c>
       <c r="AF43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3453,7 +3441,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3462,31 +3450,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="M44" t="n">
         <v>2.5</v>
@@ -3509,14 +3494,11 @@
       <c r="S44" t="n">
         <v>1</v>
       </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3532,98 +3514,149 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Acidificación del océano</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4.5</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
       <c r="AF45" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8.5</v>
       </c>
       <c r="H46" t="n">
         <v>4</v>
       </c>
+      <c r="I46" t="n">
+        <v>7</v>
+      </c>
       <c r="J46" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K46" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
         <v>8</v>
       </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>5</v>
-      </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3633,13 +3666,19 @@
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H47" t="n">
         <v>7</v>
       </c>
+      <c r="J47" t="n">
+        <v>7</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3</v>
+      </c>
       <c r="M47" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -3647,15 +3686,21 @@
       <c r="Q47" t="n">
         <v>1</v>
       </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3667,111 +3712,147 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Capas de la atmósfera y variación con la altitud</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
       <c r="S48" t="n">
         <v>1</v>
       </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
       <c r="V48" t="n">
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciclo de las rocas</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="n">
         <v>4</v>
       </c>
-      <c r="G49" t="n">
-        <v>2</v>
-      </c>
-      <c r="H49" t="n">
-        <v>4</v>
-      </c>
-      <c r="I49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J49" t="n">
-        <v>7</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>3</v>
-      </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -3783,12 +3864,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Sistemas terrestres y sus interacciones</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3801,25 +3882,25 @@
         <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G50" t="n">
         <v>6</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
-      </c>
-      <c r="L50" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
@@ -3833,20 +3914,20 @@
       <c r="Q50" t="n">
         <v>1</v>
       </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
       <c r="S50" t="n">
         <v>1</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
-      <c r="U50" t="n">
-        <v>1</v>
-      </c>
       <c r="V50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -3855,72 +3936,75 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
       </c>
       <c r="H51" t="n">
         <v>2</v>
       </c>
+      <c r="I51" t="n">
+        <v>2</v>
+      </c>
       <c r="J51" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K51" t="n">
         <v>7</v>
       </c>
-      <c r="L51" t="n">
-        <v>5</v>
-      </c>
       <c r="M51" t="n">
         <v>2.5</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
       <c r="S51" t="n">
         <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
-      <c r="U51" t="n">
-        <v>1</v>
-      </c>
       <c r="V51" t="n">
         <v>1</v>
       </c>
-      <c r="Z51" t="n">
-        <v>1</v>
-      </c>
       <c r="AF51" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -3932,41 +4016,53 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
         <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>2.5</v>
+        <v>8</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
       </c>
       <c r="H52" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
         <v>2.5</v>
       </c>
       <c r="K52" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M52" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
       <c r="Q52" t="n">
         <v>1</v>
       </c>
@@ -3987,7 +4083,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -3999,19 +4095,40 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Energía geotérmica</t>
+          <t>Uso del suelo y su degradación</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>4</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4020,14 +4137,14 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4036,26 +4153,65 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>7</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>7</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
         <v>3</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4069,60 +4225,21 @@
       <c r="D55" t="n">
         <v>3</v>
       </c>
-      <c r="E55" t="n">
-        <v>3</v>
-      </c>
-      <c r="F55" t="n">
-        <v>5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K55" t="n">
-        <v>7</v>
-      </c>
-      <c r="M55" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>3</v>
-      </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4131,54 +4248,30 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
-      </c>
-      <c r="F56" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" t="n">
         <v>2.5</v>
       </c>
-      <c r="G56" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>8</v>
-      </c>
       <c r="M56" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
       <c r="S56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
@@ -4189,19 +4282,19 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4210,19 +4303,22 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>7</v>
+      </c>
+      <c r="H57" t="n">
         <v>4</v>
       </c>
-      <c r="D57" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="I57" t="n">
         <v>6</v>
       </c>
-      <c r="H57" t="n">
-        <v>5</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2.5</v>
+      <c r="K57" t="n">
+        <v>3</v>
       </c>
       <c r="M57" t="n">
         <v>7</v>
@@ -4233,30 +4329,33 @@
       <c r="Q57" t="n">
         <v>1</v>
       </c>
-      <c r="S57" t="n">
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
         <v>1</v>
       </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Oleaje, dinámica costera y sedimentación marina</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4270,11 +4369,29 @@
       <c r="D58" t="n">
         <v>4</v>
       </c>
+      <c r="F58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>7</v>
+      </c>
       <c r="J58" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="M58" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -4283,248 +4400,170 @@
         <v>1</v>
       </c>
       <c r="AF58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Acidificación del océano</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H59" t="n">
-        <v>4</v>
-      </c>
-      <c r="I59" t="n">
-        <v>8</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K59" t="n">
-        <v>5</v>
-      </c>
-      <c r="M59" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" t="n">
-        <v>1</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1</v>
-      </c>
       <c r="AF59" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Corrientes oceánicas superficiales y profundas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
-      </c>
-      <c r="D60" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J60" t="n">
         <v>7</v>
       </c>
-      <c r="K60" t="n">
-        <v>3</v>
-      </c>
       <c r="M60" t="n">
         <v>4.5</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
       <c r="S60" t="n">
         <v>1</v>
       </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Recursos naturales renovables y no renovables</t>
+          <t>Oleaje, dinámica costera y sedimentación marina</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2</v>
-      </c>
-      <c r="F61" t="n">
-        <v>5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>6</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M61" t="n">
         <v>4.5</v>
       </c>
-      <c r="K61" t="n">
-        <v>4</v>
-      </c>
-      <c r="L61" t="n">
-        <v>5</v>
-      </c>
-      <c r="M61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
       <c r="S61" t="n">
         <v>1</v>
       </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1</v>
-      </c>
       <c r="V61" t="n">
         <v>1</v>
       </c>
-      <c r="Z61" t="n">
-        <v>1</v>
-      </c>
       <c r="AF61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" t="n">
         <v>4</v>
-      </c>
-      <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="H62" t="n">
-        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
@@ -4536,7 +4575,7 @@
         <v>1</v>
       </c>
       <c r="AF62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -4545,19 +4584,19 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sistemas terrestres y sus interacciones</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4565,118 +4604,76 @@
       </c>
       <c r="D63" t="n">
         <v>3</v>
-      </c>
-      <c r="E63" t="n">
-        <v>8</v>
       </c>
       <c r="F63" t="n">
         <v>8</v>
       </c>
-      <c r="G63" t="n">
-        <v>6</v>
-      </c>
       <c r="H63" t="n">
-        <v>2</v>
-      </c>
-      <c r="I63" t="n">
-        <v>8</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K63" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
-      <c r="S63" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
       <c r="V63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Capas de la atmósfera y variación con la altitud</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
-      </c>
-      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>6</v>
+      </c>
+      <c r="J64" t="n">
         <v>7</v>
-      </c>
-      <c r="H64" t="n">
-        <v>4</v>
-      </c>
-      <c r="I64" t="n">
-        <v>6</v>
-      </c>
-      <c r="K64" t="n">
-        <v>3</v>
       </c>
       <c r="M64" t="n">
         <v>7</v>
       </c>
-      <c r="N64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
-      <c r="T64" t="n">
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
         <v>1</v>
       </c>
       <c r="V64" t="n">
         <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -4685,19 +4682,19 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -4706,32 +4703,8 @@
       <c r="D65" t="n">
         <v>4</v>
       </c>
-      <c r="F65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2</v>
-      </c>
-      <c r="I65" t="n">
-        <v>7</v>
-      </c>
-      <c r="J65" t="n">
-        <v>7</v>
-      </c>
       <c r="M65" t="n">
-        <v>7</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="V65" t="n">
         <v>1</v>
@@ -4741,37 +4714,46 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tsunamis</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
-      </c>
-      <c r="M66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>7</v>
+      </c>
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>5</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -4780,47 +4762,26 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Uso del suelo y su degradación</t>
+          <t>Energía geotérmica</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
-      </c>
-      <c r="F67" t="n">
-        <v>5</v>
-      </c>
-      <c r="K67" t="n">
-        <v>2</v>
-      </c>
-      <c r="M67" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T67" t="n">
-        <v>1</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -4829,60 +4790,45 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Corrientes oceánicas superficiales y profundas</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
-      </c>
-      <c r="F68" t="n">
-        <v>8</v>
-      </c>
-      <c r="J68" t="n">
-        <v>7</v>
-      </c>
-      <c r="M68" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
       </c>
       <c r="AF68" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4896,14 +4842,14 @@
       <c r="D69" t="n">
         <v>4</v>
       </c>
-      <c r="M69" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V69" t="n">
+      <c r="G69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P69" t="n">
         <v>1</v>
       </c>
       <c r="AF69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -4919,7 +4865,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4928,21 +4874,15 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
-      </c>
-      <c r="E70" t="n">
-        <v>7</v>
-      </c>
-      <c r="J70" t="n">
-        <v>7</v>
-      </c>
-      <c r="N70" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="K70" t="n">
+        <v>8</v>
+      </c>
+      <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="AF70" t="n">
@@ -4962,7 +4902,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Geología y geomorfología de El Salvador</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4975,6 +4915,12 @@
       </c>
       <c r="D71" t="n">
         <v>5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
       </c>
       <c r="AF71" t="n">
         <v>5</v>
@@ -4993,7 +4939,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Ondas sísmicas, magnitud e intensidad</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5002,15 +4948,15 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
-      </c>
-      <c r="G72" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P72" t="n">
+        <v>5</v>
+      </c>
+      <c r="I72" t="n">
+        <v>6</v>
+      </c>
+      <c r="R72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
@@ -5030,7 +4976,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5044,12 +4990,6 @@
       <c r="D73" t="n">
         <v>4</v>
       </c>
-      <c r="K73" t="n">
-        <v>8</v>
-      </c>
-      <c r="T73" t="n">
-        <v>1</v>
-      </c>
       <c r="AF73" t="n">
         <v>5</v>
       </c>
@@ -5067,7 +5007,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Geología y geomorfología de El Salvador</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5076,19 +5016,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
-      </c>
-      <c r="F74" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O74" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>7</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -5097,14 +5049,14 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad</t>
+          <t>Sismicidad de El Salvador</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5113,19 +5065,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
-      </c>
-      <c r="I75" t="n">
-        <v>6</v>
-      </c>
-      <c r="R75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -5141,7 +5087,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
+          <t>Tsunamis</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5155,8 +5101,11 @@
       <c r="D76" t="n">
         <v>4</v>
       </c>
-      <c r="AF76" t="n">
-        <v>5</v>
+      <c r="M76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -5165,14 +5114,14 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sismicidad de El Salvador</t>
+          <t>Vulcanismo de El Salvador</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5203,31 +5152,82 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Vulcanismo de El Salvador</t>
+          <t>Recursos naturales renovables y no renovables</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
       <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>6</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K78" t="n">
         <v>4</v>
       </c>
-      <c r="D78" t="n">
-        <v>4</v>
+      <c r="L78" t="n">
+        <v>5</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_tierra_espacio.xlsx
+++ b/internacional/2_8/Contraste_tierra_espacio.xlsx
@@ -743,7 +743,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Capas internas de la Tierra</t>
+          <t>Capas de la atmósfera y variación con la altitud</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -756,31 +756,19 @@
       </c>
       <c r="D4" t="n">
         <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
       <c r="J4" t="n">
         <v>7</v>
       </c>
       <c r="M4" t="n">
         <v>7</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
@@ -792,7 +780,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -804,7 +792,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ciclo de las rocas</t>
+          <t>Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -818,25 +806,22 @@
       <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>4</v>
+      <c r="F5" t="n">
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
@@ -845,13 +830,10 @@
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
@@ -864,14 +846,14 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Ciclo de las rocas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -880,44 +862,32 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
@@ -933,15 +903,6 @@
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
       <c r="AF6" t="n">
         <v>3</v>
       </c>
@@ -952,14 +913,14 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -968,19 +929,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
         <v>7</v>
@@ -989,14 +959,23 @@
         <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
@@ -1013,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1022,7 +1001,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2117,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2147,77 +2126,47 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
       <c r="V25" t="n">
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2226,32 +2175,38 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
         <v>4.5</v>
       </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2261,12 +2216,12 @@
       <c r="Q26" t="n">
         <v>1</v>
       </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
@@ -2274,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2283,14 +2238,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2299,25 +2254,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
         <v>8</v>
-      </c>
-      <c r="F27" t="n">
-        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K27" t="n">
         <v>4</v>
@@ -2326,10 +2278,7 @@
         <v>7.5</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -2353,11 +2302,11 @@
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -2369,7 +2318,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2378,25 +2327,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.5</v>
       </c>
       <c r="K28" t="n">
         <v>4</v>
       </c>
+      <c r="L28" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2407,21 +2368,24 @@
       <c r="Q28" t="n">
         <v>1</v>
       </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1</v>
-      </c>
       <c r="AF28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -2433,7 +2397,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2442,25 +2406,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2468,17 +2435,17 @@
       <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="n">
         <v>1</v>
       </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
       <c r="AF29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2494,7 +2461,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2503,13 +2470,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
@@ -2517,20 +2481,14 @@
       <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
-        <v>8</v>
-      </c>
       <c r="J30" t="n">
         <v>2.5</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2538,9 +2496,6 @@
       <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
@@ -2551,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -2567,7 +2522,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2576,28 +2531,34 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
-      </c>
-      <c r="L31" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2605,20 +2566,20 @@
       <c r="Q31" t="n">
         <v>1</v>
       </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -2634,7 +2595,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2643,65 +2604,56 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
-      </c>
-      <c r="G32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5</v>
       </c>
       <c r="M32" t="n">
         <v>2.5</v>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
       <c r="AF32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -2713,7 +2665,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2722,22 +2674,25 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
         <v>6</v>
       </c>
-      <c r="I33" t="n">
-        <v>3</v>
+      <c r="H33" t="n">
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
         <v>5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.5</v>
       </c>
       <c r="M33" t="n">
         <v>7</v>
@@ -2745,7 +2700,7 @@
       <c r="P33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="n">
@@ -2754,11 +2709,14 @@
       <c r="T33" t="n">
         <v>1</v>
       </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -2774,7 +2732,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2783,22 +2741,43 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
         <v>4</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="n">
         <v>4</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K34" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
@@ -2812,8 +2791,11 @@
       <c r="T34" t="n">
         <v>1</v>
       </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
       <c r="AF34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -2829,7 +2811,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2843,14 +2825,8 @@
       <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="E35" t="n">
-        <v>2</v>
-      </c>
       <c r="G35" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
         <v>3</v>
@@ -2859,20 +2835,14 @@
         <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
@@ -2886,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -2902,7 +2872,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2911,28 +2881,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
       </c>
-      <c r="M36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
+      <c r="K36" t="n">
+        <v>5</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -2943,11 +2907,11 @@
       <c r="S36" t="n">
         <v>1</v>
       </c>
-      <c r="V36" t="n">
+      <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -2963,7 +2927,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2972,38 +2936,44 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
       </c>
       <c r="J37" t="n">
         <v>2.5</v>
       </c>
       <c r="K37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
       <c r="S37" t="n">
         <v>1</v>
       </c>
@@ -3014,11 +2984,11 @@
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -3030,7 +3000,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3039,19 +3009,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F38" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
         <v>2</v>
@@ -3060,44 +3024,32 @@
         <v>8</v>
       </c>
       <c r="J38" t="n">
+        <v>7</v>
+      </c>
+      <c r="M38" t="n">
         <v>4.5</v>
       </c>
-      <c r="K38" t="n">
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
         <v>8</v>
       </c>
-      <c r="M38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>4</v>
-      </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -3109,7 +3061,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3118,19 +3070,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
       </c>
       <c r="F39" t="n">
         <v>5</v>
       </c>
-      <c r="I39" t="n">
-        <v>7</v>
+      <c r="H39" t="n">
+        <v>2</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K39" t="n">
         <v>7</v>
@@ -3138,10 +3093,13 @@
       <c r="M39" t="n">
         <v>4.5</v>
       </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="R39" t="n">
+      <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="n">
@@ -3154,11 +3112,11 @@
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -3170,7 +3128,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3179,25 +3137,40 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.5</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
         <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
+      <c r="M40" t="n">
         <v>2.5</v>
       </c>
-      <c r="M40" t="n">
-        <v>7</v>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3209,6 +3182,9 @@
         <v>1</v>
       </c>
       <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="V40" t="n">
@@ -3219,7 +3195,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3231,7 +3207,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3240,41 +3216,29 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
-      </c>
-      <c r="E41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F41" t="n">
         <v>5</v>
       </c>
-      <c r="G41" t="n">
-        <v>2</v>
-      </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J41" t="n">
         <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
@@ -3288,7 +3252,7 @@
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -3304,7 +3268,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3313,49 +3277,43 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M42" t="n">
         <v>7</v>
       </c>
-      <c r="J42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K42" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
       <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3371,7 +3329,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3380,25 +3338,28 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" t="n">
         <v>4</v>
       </c>
-      <c r="D43" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" t="n">
-        <v>3</v>
-      </c>
       <c r="F43" t="n">
         <v>5</v>
       </c>
-      <c r="H43" t="n">
+      <c r="G43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
         <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3</v>
       </c>
       <c r="M43" t="n">
         <v>2.5</v>
@@ -3409,7 +3370,7 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="R43" t="n">
@@ -3418,14 +3379,14 @@
       <c r="S43" t="n">
         <v>1</v>
       </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
-      <c r="Z43" t="n">
-        <v>1</v>
-      </c>
       <c r="AF43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3441,7 +3402,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3450,55 +3411,49 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
       </c>
-      <c r="F44" t="n">
-        <v>2.5</v>
-      </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" t="n">
         <v>4.5</v>
       </c>
-      <c r="M44" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
       <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3514,7 +3469,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3528,20 +3483,29 @@
       <c r="D45" t="n">
         <v>4</v>
       </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5</v>
+      </c>
       <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
         <v>4</v>
       </c>
-      <c r="I45" t="n">
-        <v>8</v>
-      </c>
       <c r="J45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M45" t="n">
         <v>2.5</v>
       </c>
-      <c r="K45" t="n">
-        <v>5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>4.5</v>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -3552,10 +3516,10 @@
       <c r="S45" t="n">
         <v>1</v>
       </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
       <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="n">
         <v>1</v>
       </c>
       <c r="AF45" t="n">
@@ -3563,7 +3527,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
@@ -3575,7 +3539,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3584,32 +3548,35 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G46" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>4.5</v>
       </c>
-      <c r="K46" t="n">
-        <v>6</v>
-      </c>
       <c r="M46" t="n">
         <v>2.5</v>
       </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
@@ -3625,17 +3592,11 @@
       <c r="S46" t="n">
         <v>1</v>
       </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
       <c r="V46" t="n">
         <v>1</v>
       </c>
-      <c r="Z46" t="n">
-        <v>1</v>
-      </c>
       <c r="AF46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3651,7 +3612,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3660,32 +3621,32 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M47" t="n">
         <v>4.5</v>
       </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
       <c r="S47" t="n">
         <v>1</v>
       </c>
@@ -3696,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -3712,7 +3673,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3721,33 +3682,33 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
         <v>4.5</v>
       </c>
       <c r="K48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M48" t="n">
         <v>2.5</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>1</v>
       </c>
       <c r="P48" t="n">
@@ -3768,8 +3729,11 @@
       <c r="V48" t="n">
         <v>1</v>
       </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -3785,7 +3749,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3794,50 +3758,32 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
       </c>
-      <c r="G49" t="n">
-        <v>3</v>
-      </c>
       <c r="H49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
         <v>4.5</v>
       </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
       <c r="S49" t="n">
         <v>1</v>
       </c>
@@ -3848,11 +3794,11 @@
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -3864,7 +3810,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sistemas terrestres y sus interacciones</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3873,41 +3819,35 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>5</v>
+      </c>
+      <c r="M50" t="n">
         <v>2.5</v>
       </c>
-      <c r="K50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
@@ -3927,23 +3867,23 @@
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3952,59 +3892,35 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>7</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
       <c r="S51" t="n">
         <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
-      <c r="V51" t="n">
-        <v>1</v>
-      </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -4016,7 +3932,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4025,34 +3941,34 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
       </c>
       <c r="F52" t="n">
+        <v>5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
         <v>8</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" t="n">
-        <v>3</v>
-      </c>
-      <c r="I52" t="n">
-        <v>5</v>
       </c>
       <c r="J52" t="n">
         <v>2.5</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M52" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N52" t="n">
         <v>1</v>
@@ -4079,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="AF52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4095,7 +4011,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Uso del suelo y su degradación</t>
+          <t>Sistemas terrestres y sus interacciones</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4104,23 +4020,53 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>8</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="G53" t="n">
+        <v>6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.5</v>
       </c>
       <c r="K53" t="n">
         <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
@@ -4128,28 +4074,28 @@
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -4161,24 +4107,30 @@
       <c r="F54" t="n">
         <v>2.5</v>
       </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
       <c r="H54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K54" t="n">
         <v>7</v>
       </c>
       <c r="M54" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
@@ -4195,11 +4147,11 @@
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -4211,12 +4163,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
+          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -4225,26 +4177,77 @@
       <c r="D55" t="n">
         <v>3</v>
       </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>3</v>
+      </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Uso del suelo y su degradación</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4253,25 +4256,19 @@
       <c r="D56" t="n">
         <v>4</v>
       </c>
-      <c r="E56" t="n">
-        <v>6</v>
-      </c>
-      <c r="H56" t="n">
-        <v>5</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.5</v>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>7</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
@@ -4282,19 +4279,19 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4303,27 +4300,30 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
-      </c>
-      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H57" t="n">
         <v>7</v>
       </c>
-      <c r="H57" t="n">
-        <v>4</v>
-      </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.5</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>7</v>
-      </c>
-      <c r="N57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O57" t="n">
         <v>1</v>
       </c>
       <c r="Q57" t="n">
@@ -4332,6 +4332,9 @@
       <c r="R57" t="n">
         <v>1</v>
       </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
@@ -4339,11 +4342,11 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -4355,7 +4358,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4364,147 +4367,147 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2</v>
-      </c>
-      <c r="I58" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" t="n">
-        <v>7</v>
-      </c>
-      <c r="M58" t="n">
-        <v>7</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="n">
-        <v>1</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Acidificación del océano</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M59" t="n">
         <v>7</v>
       </c>
-      <c r="D59" t="n">
-        <v>7</v>
-      </c>
-      <c r="H59" t="n">
-        <v>7</v>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
       <c r="AF59" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Corrientes oceánicas superficiales y profundas</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
-      </c>
-      <c r="F60" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="n">
         <v>7</v>
       </c>
+      <c r="H60" t="n">
+        <v>4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>6</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3</v>
+      </c>
       <c r="M60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1</v>
-      </c>
-      <c r="S60" t="n">
+        <v>7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="V60" t="n">
         <v>1</v>
       </c>
       <c r="AF60" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oleaje, dinámica costera y sedimentación marina</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4513,11 +4516,29 @@
       <c r="D61" t="n">
         <v>4</v>
       </c>
+      <c r="F61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" t="n">
+        <v>7</v>
+      </c>
       <c r="J61" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -4526,170 +4547,149 @@
         <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Acidificación del océano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>7</v>
+      </c>
+      <c r="D62" t="n">
+        <v>7</v>
+      </c>
+      <c r="H62" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
           <t>sin_referente</t>
         </is>
       </c>
-      <c r="C62" t="n">
-        <v>5</v>
-      </c>
-      <c r="D62" t="n">
-        <v>5</v>
-      </c>
-      <c r="H62" t="n">
-        <v>4</v>
-      </c>
-      <c r="J62" t="n">
-        <v>7</v>
-      </c>
-      <c r="K62" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>1</v>
-      </c>
-      <c r="T62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>sin_referente</t>
-        </is>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Corrientes oceánicas superficiales y profundas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
-      </c>
-      <c r="D63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F63" t="n">
         <v>8</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="S63" t="n">
         <v>1</v>
       </c>
       <c r="V63" t="n">
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Capas de la atmósfera y variación con la altitud</t>
+          <t>Oleaje, dinámica costera y sedimentación marina</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
           <t>sin_referente</t>
         </is>
       </c>
-      <c r="C64" t="n">
-        <v>3</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3</v>
-      </c>
-      <c r="G64" t="n">
-        <v>6</v>
-      </c>
-      <c r="J64" t="n">
-        <v>7</v>
-      </c>
-      <c r="M64" t="n">
-        <v>7</v>
-      </c>
-      <c r="P64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>sin_referente</t>
-        </is>
-      </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4698,19 +4698,31 @@
         </is>
       </c>
       <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" t="n">
         <v>4</v>
       </c>
-      <c r="D65" t="n">
-        <v>4</v>
-      </c>
-      <c r="M65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V65" t="n">
+      <c r="J65" t="n">
+        <v>7</v>
+      </c>
+      <c r="K65" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -4719,14 +4731,14 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4735,25 +4747,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
-      </c>
-      <c r="E66" t="n">
-        <v>7</v>
-      </c>
-      <c r="J66" t="n">
-        <v>7</v>
-      </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="M66" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -4769,7 +4775,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Energía geotérmica</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4778,10 +4784,25 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>7</v>
+      </c>
+      <c r="J67" t="n">
+        <v>7</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>5</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -4790,14 +4811,14 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Energía geotérmica</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4806,13 +4827,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -4821,14 +4839,14 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4837,16 +4855,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
-      </c>
-      <c r="G69" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF69" t="n">
         <v>5</v>
@@ -4865,7 +4877,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4879,10 +4891,10 @@
       <c r="D70" t="n">
         <v>4</v>
       </c>
-      <c r="K70" t="n">
-        <v>8</v>
-      </c>
-      <c r="T70" t="n">
+      <c r="G70" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P70" t="n">
         <v>1</v>
       </c>
       <c r="AF70" t="n">
@@ -4902,7 +4914,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Geología y geomorfología de El Salvador</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4911,15 +4923,15 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
-      </c>
-      <c r="F71" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O71" t="n">
+        <v>4</v>
+      </c>
+      <c r="K71" t="n">
+        <v>8</v>
+      </c>
+      <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="AF71" t="n">
@@ -4939,7 +4951,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad</t>
+          <t>Geología y geomorfología de El Salvador</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4953,10 +4965,10 @@
       <c r="D72" t="n">
         <v>5</v>
       </c>
-      <c r="I72" t="n">
-        <v>6</v>
-      </c>
-      <c r="R72" t="n">
+      <c r="F72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
@@ -4976,7 +4988,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
+          <t>Ondas sísmicas, magnitud e intensidad</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4985,10 +4997,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>6</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
       </c>
       <c r="AF73" t="n">
         <v>5</v>
@@ -5007,7 +5025,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5021,26 +5039,8 @@
       <c r="D74" t="n">
         <v>4</v>
       </c>
-      <c r="H74" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" t="n">
-        <v>7</v>
-      </c>
-      <c r="K74" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>1</v>
-      </c>
-      <c r="S74" t="n">
-        <v>1</v>
-      </c>
-      <c r="T74" t="n">
-        <v>1</v>
-      </c>
       <c r="AF74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_tierra_espacio.xlsx
+++ b/internacional/2_8/Contraste_tierra_espacio.xlsx
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
         <v>8</v>
@@ -2381,16 +2381,16 @@
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>

--- a/internacional/2_8/Contraste_tierra_espacio.xlsx
+++ b/internacional/2_8/Contraste_tierra_espacio.xlsx
@@ -2665,7 +2665,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2674,53 +2674,53 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
         <v>7</v>
       </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
       <c r="J33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K33" t="n">
         <v>7</v>
       </c>
-      <c r="K33" t="n">
-        <v>5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M33" t="n">
-        <v>7</v>
-      </c>
-      <c r="P33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -2732,7 +2732,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2741,40 +2741,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7.5</v>
       </c>
       <c r="M34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -2782,20 +2770,20 @@
       <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -2811,7 +2799,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2820,27 +2808,45 @@
         </is>
       </c>
       <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
         <v>4</v>
       </c>
-      <c r="D35" t="n">
-        <v>4</v>
+      <c r="F35" t="n">
+        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>6</v>
       </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
       </c>
       <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
@@ -2872,7 +2878,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2886,19 +2892,22 @@
       <c r="D36" t="n">
         <v>4</v>
       </c>
-      <c r="H36" t="n">
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="n">
         <v>3</v>
       </c>
-      <c r="I36" t="n">
-        <v>4</v>
-      </c>
       <c r="J36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
         <v>7</v>
       </c>
-      <c r="K36" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="P36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
@@ -2910,8 +2919,11 @@
       <c r="T36" t="n">
         <v>1</v>
       </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
       <c r="AF36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -2927,7 +2939,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2941,32 +2953,17 @@
       <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>2</v>
-      </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
@@ -2978,9 +2975,6 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
@@ -3000,7 +2994,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3009,10 +3003,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>3</v>
@@ -3021,13 +3018,19 @@
         <v>2</v>
       </c>
       <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" t="n">
-        <v>7</v>
-      </c>
       <c r="M38" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3041,11 +3044,14 @@
       <c r="S38" t="n">
         <v>1</v>
       </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
       <c r="V38" t="n">
         <v>1</v>
       </c>
       <c r="AF38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -3061,7 +3067,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3075,48 +3081,42 @@
       <c r="D39" t="n">
         <v>3</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>5</v>
-      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
+      <c r="I39" t="n">
+        <v>8</v>
+      </c>
       <c r="J39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K39" t="n">
         <v>7</v>
       </c>
       <c r="M39" t="n">
         <v>4.5</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -3128,7 +3128,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3137,50 +3137,38 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="n">
         <v>2.5</v>
       </c>
-      <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>8</v>
-      </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
+        <v>7</v>
+      </c>
+      <c r="M40" t="n">
         <v>4.5</v>
       </c>
-      <c r="K40" t="n">
-        <v>8</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
@@ -3191,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3207,7 +3195,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3216,29 +3204,47 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M41" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="n">
         <v>1</v>
       </c>
@@ -3252,11 +3258,11 @@
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -3268,7 +3274,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3277,30 +3283,27 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="K42" t="n">
+        <v>7</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
@@ -3309,11 +3312,14 @@
       <c r="S42" t="n">
         <v>1</v>
       </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
       <c r="V42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3329,7 +3335,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3338,55 +3344,43 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" t="n">
         <v>4</v>
       </c>
-      <c r="F43" t="n">
-        <v>5</v>
-      </c>
       <c r="G43" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
         <v>4</v>
-      </c>
-      <c r="J43" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" t="n">
-        <v>3</v>
-      </c>
-      <c r="M43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>5</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3402,7 +3396,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3417,13 +3411,16 @@
         <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
       </c>
-      <c r="H44" t="n">
-        <v>7</v>
+      <c r="I44" t="n">
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>7</v>
@@ -3432,15 +3429,18 @@
         <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="n">
@@ -3453,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3478,52 +3478,49 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="F45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" t="n">
+      <c r="M45" t="n">
         <v>4.5</v>
       </c>
-      <c r="M45" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
       <c r="S45" t="n">
         <v>1</v>
       </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
       <c r="V45" t="n">
         <v>1</v>
       </c>
-      <c r="Z45" t="n">
-        <v>1</v>
-      </c>
       <c r="AF45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3539,7 +3536,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3548,25 +3545,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H46" t="n">
         <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>4.5</v>
@@ -3580,9 +3574,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
@@ -3595,8 +3586,11 @@
       <c r="V46" t="n">
         <v>1</v>
       </c>
+      <c r="Z46" t="n">
+        <v>1</v>
+      </c>
       <c r="AF46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3612,7 +3606,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3621,25 +3615,40 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M47" t="n">
         <v>2.5</v>
       </c>
-      <c r="K47" t="n">
-        <v>5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>4.5</v>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
@@ -3650,18 +3659,15 @@
       <c r="S47" t="n">
         <v>1</v>
       </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
       <c r="AF47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -3673,7 +3679,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3682,38 +3688,26 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
-      </c>
-      <c r="F48" t="n">
-        <v>8</v>
-      </c>
-      <c r="G48" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
         <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5</v>
+      </c>
+      <c r="M48" t="n">
         <v>4.5</v>
       </c>
-      <c r="K48" t="n">
-        <v>6</v>
-      </c>
-      <c r="M48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1</v>
-      </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
@@ -3729,15 +3723,12 @@
       <c r="V48" t="n">
         <v>1</v>
       </c>
-      <c r="Z48" t="n">
-        <v>1</v>
-      </c>
       <c r="AF48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -3749,7 +3740,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3758,32 +3749,44 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>8.5</v>
       </c>
       <c r="H49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="n">
         <v>7</v>
       </c>
       <c r="J49" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M49" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
       <c r="S49" t="n">
         <v>1</v>
       </c>
@@ -3791,6 +3794,9 @@
         <v>1</v>
       </c>
       <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z49" t="n">
         <v>1</v>
       </c>
       <c r="AF49" t="n">
@@ -3798,7 +3804,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -3810,7 +3816,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3819,44 +3825,32 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" t="n">
         <v>3</v>
       </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
       <c r="H50" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
+        <v>7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" t="n">
         <v>4.5</v>
       </c>
-      <c r="K50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="O50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
       <c r="S50" t="n">
         <v>1</v>
       </c>
@@ -3867,11 +3861,11 @@
         <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -3883,7 +3877,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3892,35 +3886,59 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K51" t="n">
         <v>5</v>
       </c>
+      <c r="M51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
       <c r="S51" t="n">
         <v>1</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
       <c r="AF51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -3932,7 +3950,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3946,52 +3964,22 @@
       <c r="D52" t="n">
         <v>4</v>
       </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>5</v>
-      </c>
-      <c r="G52" t="n">
-        <v>3</v>
-      </c>
       <c r="H52" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
         <v>5</v>
       </c>
-      <c r="M52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1</v>
-      </c>
       <c r="Q52" t="n">
         <v>1</v>
       </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
       <c r="S52" t="n">
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" t="n">
         <v>1</v>
       </c>
       <c r="AF52" t="n">
@@ -3999,7 +3987,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
@@ -4011,7 +3999,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sistemas terrestres y sus interacciones</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4020,19 +4008,19 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
         <v>3</v>
-      </c>
-      <c r="D53" t="n">
-        <v>3</v>
-      </c>
-      <c r="E53" t="n">
-        <v>8</v>
-      </c>
-      <c r="F53" t="n">
-        <v>8</v>
-      </c>
-      <c r="G53" t="n">
-        <v>6</v>
       </c>
       <c r="H53" t="n">
         <v>2</v>
@@ -4044,10 +4032,10 @@
         <v>2.5</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M53" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N53" t="n">
         <v>1</v>
@@ -4074,23 +4062,23 @@
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Sistemas terrestres y sus interacciones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4099,31 +4087,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8</v>
       </c>
       <c r="F54" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>8</v>
+      </c>
+      <c r="J54" t="n">
         <v>2.5</v>
       </c>
-      <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
@@ -4147,23 +4141,23 @@
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4172,38 +4166,32 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" t="n">
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M55" t="n">
         <v>2.5</v>
       </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
@@ -4226,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4242,7 +4230,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Uso del suelo y su degradación</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4251,21 +4239,33 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>7</v>
+      </c>
+      <c r="H56" t="n">
         <v>4</v>
       </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="F56" t="n">
-        <v>5</v>
+      <c r="I56" t="n">
+        <v>6</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O56" t="n">
+        <v>7</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
         <v>1</v>
       </c>
       <c r="T56" t="n">
@@ -4291,37 +4291,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>2.5</v>
       </c>
       <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="n">
         <v>7</v>
       </c>
-      <c r="I57" t="n">
-        <v>3</v>
-      </c>
       <c r="J57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K57" t="n">
         <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
@@ -4335,35 +4332,32 @@
       <c r="S57" t="n">
         <v>1</v>
       </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
+          <t>alineado</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
           <t>adelantado</t>
-        </is>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
+          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -4372,26 +4366,77 @@
       <c r="D58" t="n">
         <v>3</v>
       </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>3</v>
+      </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Uso del suelo y su degradación</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -4400,94 +4445,55 @@
       <c r="D59" t="n">
         <v>4</v>
       </c>
-      <c r="E59" t="n">
-        <v>6</v>
-      </c>
-      <c r="H59" t="n">
-        <v>5</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2.5</v>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>7</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="V59" t="n">
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
-      </c>
-      <c r="E60" t="n">
-        <v>7</v>
-      </c>
-      <c r="H60" t="n">
-        <v>4</v>
-      </c>
-      <c r="I60" t="n">
-        <v>6</v>
-      </c>
-      <c r="K60" t="n">
         <v>3</v>
       </c>
-      <c r="M60" t="n">
-        <v>7</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>5</v>
-      </c>
       <c r="AG60" t="inlineStr">
         <is>
           <t>sin_referente</t>
@@ -4495,75 +4501,51 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Acidificación del océano</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
-      </c>
-      <c r="F61" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
-      </c>
-      <c r="I61" t="n">
         <v>7</v>
       </c>
-      <c r="J61" t="n">
-        <v>7</v>
-      </c>
-      <c r="M61" t="n">
-        <v>7</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
-      <c r="S61" t="n">
-        <v>1</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1</v>
-      </c>
       <c r="AF61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Acidificación del océano</t>
+          <t>Corrientes oceánicas superficiales y profundas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4572,15 +4554,24 @@
         </is>
       </c>
       <c r="C62" t="n">
+        <v>9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
+      <c r="J62" t="n">
         <v>7</v>
       </c>
-      <c r="D62" t="n">
-        <v>7</v>
-      </c>
-      <c r="H62" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q62" t="n">
+      <c r="M62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
@@ -4588,7 +4579,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
@@ -4600,7 +4591,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Corrientes oceánicas superficiales y profundas</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4609,18 +4600,27 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
-      </c>
-      <c r="F63" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" t="n">
+        <v>5</v>
       </c>
       <c r="J63" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M63" t="n">
         <v>7</v>
       </c>
-      <c r="M63" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O63" t="n">
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="S63" t="n">
@@ -4630,16 +4630,16 @@
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>

--- a/internacional/2_8/Contraste_tierra_espacio.xlsx
+++ b/internacional/2_8/Contraste_tierra_espacio.xlsx
@@ -630,7 +630,7 @@
         <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>4.5</v>
@@ -920,7 +920,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Eclipses solares y lunares</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -929,70 +929,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.5</v>
-      </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1008,7 +981,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eclipses solares y lunares</t>
+          <t>El Sol como estrella</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1017,32 +990,38 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
@@ -1053,7 +1032,7 @@
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1069,7 +1048,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>El Sol como estrella</t>
+          <t>Fósiles y su formación</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1078,13 +1057,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -1093,13 +1075,16 @@
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1120,7 +1105,7 @@
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1136,7 +1121,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fósiles y su formación</t>
+          <t>Fuentes de energía renovables y no renovables</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1145,19 +1130,19 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
@@ -1166,10 +1151,13 @@
         <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1189,11 +1177,17 @@
       <c r="T10" t="n">
         <v>1</v>
       </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
       <c r="AF10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1209,7 +1203,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fuentes de energía renovables y no renovables</t>
+          <t>Galaxias y escala del universo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1218,37 +1212,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1256,26 +1238,17 @@
       <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -1291,7 +1264,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Galaxias y escala del universo</t>
+          <t>Impacto de las actividades humanas en los recursos</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1300,43 +1273,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
       <c r="V12" t="n">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -1352,7 +1337,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Impacto de las actividades humanas en los recursos</t>
+          <t>Límites de placas: convergentes, divergentes y transformantes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1361,55 +1346,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5</v>
-      </c>
       <c r="M13" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
       <c r="V13" t="n">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -1425,7 +1392,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Límites de placas: convergentes, divergentes y transformantes</t>
+          <t>Origen del magma y vulcanismo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1434,16 +1401,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
       </c>
       <c r="J14" t="n">
         <v>7</v>
@@ -1451,10 +1418,10 @@
       <c r="M14" t="n">
         <v>7</v>
       </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
@@ -1480,7 +1447,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Origen del magma y vulcanismo</t>
+          <t>Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1489,37 +1456,49 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5</v>
       </c>
       <c r="M15" t="n">
         <v>7</v>
       </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
         <v>1</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -1535,7 +1514,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Calidad y tratamiento del agua</t>
+          <t>El océano: propiedades del agua de mar y zonas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1552,17 +1531,11 @@
       <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
         <v>7</v>
       </c>
-      <c r="L16" t="n">
-        <v>5</v>
+      <c r="J16" t="n">
+        <v>2.5</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
@@ -1570,16 +1543,10 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="V16" t="n">
@@ -1602,7 +1569,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>El océano: propiedades del agua de mar y zonas</t>
+          <t>Registro fósil y cambios ambientales del pasado</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1616,25 +1583,31 @@
       <c r="D17" t="n">
         <v>3</v>
       </c>
-      <c r="F17" t="n">
-        <v>5</v>
-      </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
       <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
@@ -1657,7 +1630,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Registro fósil y cambios ambientales del pasado</t>
+          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1666,25 +1639,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -1695,14 +1671,14 @@
       <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
       <c r="V18" t="n">
         <v>1</v>
       </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
       <c r="AF18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -1718,7 +1694,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Riesgo de desastre: amenaza, vulnerabilidad y prevención</t>
+          <t>Sismos y fallas geológicas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1739,7 +1715,7 @@
         <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
         <v>2.5</v>
@@ -1762,9 +1738,6 @@
       <c r="V19" t="n">
         <v>1</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1</v>
-      </c>
       <c r="AF19" t="n">
         <v>2</v>
       </c>
@@ -1782,7 +1755,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sismos y fallas geológicas</t>
+          <t>Tectónica de placas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1791,29 +1764,41 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
+      <c r="G20" t="n">
+        <v>6</v>
+      </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
         <v>2.5</v>
       </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
@@ -1827,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1843,7 +1828,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tectónica de placas</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1852,41 +1837,35 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
         <v>8</v>
       </c>
-      <c r="G21" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5</v>
-      </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
       <c r="P21" t="n">
         <v>1</v>
       </c>
@@ -1906,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -1922,7 +1901,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Volcanes: estructura, tipos y productos</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1931,39 +1910,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" t="n">
-        <v>2</v>
+      <c r="F22" t="n">
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O22" t="n">
         <v>1</v>
       </c>
       <c r="R22" t="n">
@@ -1972,14 +1933,8 @@
       <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -1995,56 +1950,80 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Volcanes: estructura, tipos y productos</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
-      <c r="I23" t="n">
-        <v>5</v>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>2.5</v>
       </c>
+      <c r="K23" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M23" t="n">
+        <v>7</v>
+      </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
       <c r="AF23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2053,28 +2032,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="G24" t="n">
-        <v>6</v>
-      </c>
       <c r="H24" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
-      </c>
-      <c r="L24" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
         <v>7</v>
@@ -2082,19 +2052,10 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
       <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="n">
@@ -2105,7 +2066,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -2117,7 +2078,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2126,47 +2087,77 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
         <v>3</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L25" t="n">
         <v>3</v>
       </c>
-      <c r="F25" t="n">
-        <v>8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>7</v>
-      </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
       <c r="V25" t="n">
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2175,38 +2166,32 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
+      <c r="J26" t="n">
         <v>2.5</v>
       </c>
-      <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.5</v>
+      <c r="K26" t="n">
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M26" t="n">
         <v>4.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2216,12 +2201,12 @@
       <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
       <c r="U26" t="n">
         <v>1</v>
       </c>
@@ -2229,7 +2214,7 @@
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2238,14 +2223,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2254,32 +2239,41 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
         <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
         <v>4.5</v>
       </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
@@ -2289,6 +2283,9 @@
       <c r="Q27" t="n">
         <v>1</v>
       </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
@@ -2301,8 +2298,11 @@
       <c r="V27" t="n">
         <v>1</v>
       </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
       <c r="AF27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>4.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
         <v>7.5</v>
@@ -2421,7 +2421,7 @@
         <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>7</v>
@@ -2485,7 +2485,7 @@
         <v>2.5</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
         <v>4.5</v>
@@ -2619,7 +2619,7 @@
         <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>5</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
         <v>2.5</v>
       </c>
       <c r="K33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>4.5</v>
@@ -3155,7 +3155,7 @@
         <v>2.5</v>
       </c>
       <c r="K40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
         <v>4.5</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3228,7 +3228,7 @@
         <v>4.5</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
         <v>2.5</v>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
         <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
         <v>2.5</v>
@@ -3565,6 +3565,9 @@
       <c r="J46" t="n">
         <v>4.5</v>
       </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
       <c r="M46" t="n">
         <v>2.5</v>
       </c>
@@ -3583,6 +3586,9 @@
       <c r="S46" t="n">
         <v>1</v>
       </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
       <c r="V46" t="n">
         <v>1</v>
       </c>
@@ -3638,6 +3644,9 @@
       <c r="J47" t="n">
         <v>4.5</v>
       </c>
+      <c r="K47" t="n">
+        <v>2</v>
+      </c>
       <c r="M47" t="n">
         <v>2.5</v>
       </c>
@@ -3659,6 +3668,9 @@
       <c r="S47" t="n">
         <v>1</v>
       </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
@@ -3770,7 +3782,7 @@
         <v>4.5</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
         <v>2.5</v>
@@ -3840,7 +3852,7 @@
         <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
         <v>4.5</v>
@@ -3907,7 +3919,7 @@
         <v>4.5</v>
       </c>
       <c r="K51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
         <v>2.5</v>
@@ -4187,7 +4199,7 @@
         <v>4.5</v>
       </c>
       <c r="K55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
         <v>2.5</v>
@@ -4317,6 +4329,9 @@
       <c r="J57" t="n">
         <v>7</v>
       </c>
+      <c r="K57" t="n">
+        <v>7</v>
+      </c>
       <c r="M57" t="n">
         <v>7</v>
       </c>
@@ -4332,6 +4347,9 @@
       <c r="S57" t="n">
         <v>1</v>
       </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
@@ -5182,7 +5200,7 @@
         <v>4.5</v>
       </c>
       <c r="K78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L78" t="n">
         <v>5</v>

--- a/internacional/2_8/Contraste_tierra_espacio.xlsx
+++ b/internacional/2_8/Contraste_tierra_espacio.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH79"/>
+  <dimension ref="A1:AH80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
@@ -1755,7 +1755,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tectónica de placas</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1764,38 +1764,35 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
         <v>8</v>
       </c>
-      <c r="G20" t="n">
-        <v>6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
@@ -1808,11 +1805,14 @@
       <c r="S20" t="n">
         <v>1</v>
       </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
       <c r="V20" t="n">
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Volcanes: estructura, tipos y productos</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,39 +1837,21 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="n">
-        <v>2</v>
+      <c r="F21" t="n">
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
@@ -1878,14 +1860,8 @@
       <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -1901,56 +1877,80 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Volcanes: estructura, tipos y productos</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
       </c>
-      <c r="I22" t="n">
-        <v>5</v>
+      <c r="G22" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>2.5</v>
       </c>
+      <c r="K22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1959,28 +1959,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
-      <c r="G23" t="n">
-        <v>6</v>
-      </c>
       <c r="H23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
         <v>7</v>
@@ -1988,19 +1979,10 @@
       <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
       <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
@@ -2011,7 +1993,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -2023,7 +2005,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2032,53 +2014,77 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="n">
-        <v>8</v>
-      </c>
-      <c r="H24" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
       <c r="M24" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="n">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2087,38 +2093,32 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="H25" t="n">
         <v>3</v>
       </c>
-      <c r="F25" t="n">
+      <c r="J25" t="n">
         <v>2.5</v>
       </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.5</v>
+      <c r="K25" t="n">
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="M25" t="n">
         <v>4.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
@@ -2128,12 +2128,12 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2150,14 +2150,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2166,32 +2166,41 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
         <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M26" t="n">
         <v>4.5</v>
       </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2201,6 +2210,9 @@
       <c r="Q26" t="n">
         <v>1</v>
       </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
@@ -2213,8 +2225,11 @@
       <c r="V26" t="n">
         <v>1</v>
       </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2230,7 +2245,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2239,25 +2254,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>4.5</v>
@@ -2266,10 +2278,10 @@
         <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
@@ -2283,9 +2295,6 @@
       <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
@@ -2298,11 +2307,8 @@
       <c r="V27" t="n">
         <v>1</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1</v>
-      </c>
       <c r="AF27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2311,14 +2317,14 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2327,37 +2333,25 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
-      </c>
-      <c r="E28" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" t="n">
         <v>8</v>
-      </c>
-      <c r="F28" t="n">
-        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
         <v>2</v>
       </c>
-      <c r="L28" t="n">
-        <v>7.5</v>
-      </c>
       <c r="M28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2368,20 +2362,17 @@
       <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
       <c r="AF28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -2390,14 +2381,14 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2406,46 +2397,43 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
       </c>
       <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
         <v>3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>7</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2461,7 +2449,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2470,10 +2458,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
@@ -2481,6 +2472,9 @@
       <c r="H30" t="n">
         <v>2</v>
       </c>
+      <c r="I30" t="n">
+        <v>8</v>
+      </c>
       <c r="J30" t="n">
         <v>2.5</v>
       </c>
@@ -2488,7 +2482,10 @@
         <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2496,6 +2493,9 @@
       <c r="Q30" t="n">
         <v>1</v>
       </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2531,28 +2531,25 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
-      <c r="G31" t="n">
-        <v>6</v>
-      </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
-      <c r="I31" t="n">
-        <v>8</v>
-      </c>
       <c r="J31" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5</v>
       </c>
       <c r="M31" t="n">
         <v>2.5</v>
@@ -2560,30 +2557,30 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -2595,7 +2592,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2604,53 +2601,50 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="D32" t="n">
+      <c r="J32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
         <v>3</v>
       </c>
-      <c r="F32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>7</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>7</v>
-      </c>
       <c r="AG32" t="inlineStr">
         <is>
           <t>adelantado</t>
@@ -2658,14 +2652,14 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2674,53 +2668,53 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
       </c>
       <c r="H33" t="n">
         <v>7</v>
       </c>
-      <c r="I33" t="n">
-        <v>3</v>
-      </c>
       <c r="J33" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>7.5</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O33" t="n">
+        <v>7</v>
+      </c>
+      <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -2732,7 +2726,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2741,28 +2735,40 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K34" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -2770,20 +2776,20 @@
       <c r="Q34" t="n">
         <v>1</v>
       </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -2799,7 +2805,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2812,41 +2818,23 @@
       </c>
       <c r="D35" t="n">
         <v>5</v>
-      </c>
-      <c r="E35" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" t="n">
-        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>6</v>
       </c>
-      <c r="H35" t="n">
-        <v>4</v>
-      </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
@@ -2878,7 +2866,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2892,22 +2880,19 @@
       <c r="D36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" t="n">
-        <v>6</v>
+      <c r="H36" t="n">
+        <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
         <v>5</v>
       </c>
-      <c r="M36" t="n">
-        <v>7</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
@@ -2919,11 +2904,8 @@
       <c r="T36" t="n">
         <v>1</v>
       </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
       <c r="AF36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -2939,7 +2921,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2953,17 +2935,32 @@
       <c r="D37" t="n">
         <v>4</v>
       </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3</v>
+      </c>
       <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
         <v>3</v>
       </c>
-      <c r="I37" t="n">
-        <v>4</v>
-      </c>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
@@ -2975,6 +2972,9 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
@@ -2994,7 +2994,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3003,13 +3003,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
         <v>3</v>
@@ -3018,19 +3015,13 @@
         <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3042,9 +3033,6 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="n">
@@ -3067,7 +3055,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3081,38 +3069,44 @@
       <c r="D39" t="n">
         <v>3</v>
       </c>
-      <c r="G39" t="n">
+      <c r="E39" t="n">
         <v>3</v>
       </c>
+      <c r="F39" t="n">
+        <v>5</v>
+      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
-      <c r="I39" t="n">
-        <v>8</v>
-      </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
       </c>
       <c r="M39" t="n">
         <v>4.5</v>
       </c>
-      <c r="P39" t="n">
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3128,7 +3122,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3137,38 +3131,50 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>2.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
       </c>
       <c r="H40" t="n">
         <v>2</v>
       </c>
+      <c r="I40" t="n">
+        <v>8</v>
+      </c>
       <c r="J40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
         <v>2.5</v>
       </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>4.5</v>
-      </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
@@ -3179,11 +3185,11 @@
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3195,7 +3201,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3204,40 +3210,25 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5</v>
-      </c>
-      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
         <v>2.5</v>
       </c>
-      <c r="G41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2</v>
-      </c>
-      <c r="I41" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K41" t="n">
-        <v>2</v>
-      </c>
       <c r="M41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3249,9 +3240,6 @@
         <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="V41" t="n">
@@ -3262,19 +3250,19 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3283,29 +3271,41 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
       </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3344,25 +3344,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
       </c>
       <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7</v>
+      </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" t="n">
         <v>3</v>
       </c>
-      <c r="H43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" t="n">
-        <v>2.5</v>
-      </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>4.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -3370,17 +3376,17 @@
       <c r="Q43" t="n">
         <v>1</v>
       </c>
-      <c r="R43" t="n">
-        <v>1</v>
-      </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3396,7 +3402,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3405,25 +3411,25 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K44" t="n">
         <v>2</v>
@@ -3437,7 +3443,7 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
@@ -3452,8 +3458,11 @@
       <c r="V44" t="n">
         <v>1</v>
       </c>
+      <c r="Z44" t="n">
+        <v>1</v>
+      </c>
       <c r="AF44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3469,7 +3478,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3478,38 +3487,50 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
+      <c r="F45" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
       <c r="S45" t="n">
         <v>1</v>
       </c>
@@ -3520,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3536,7 +3557,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3550,33 +3571,21 @@
       <c r="D46" t="n">
         <v>4</v>
       </c>
-      <c r="E46" t="n">
-        <v>3</v>
-      </c>
-      <c r="F46" t="n">
-        <v>5</v>
-      </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5</v>
+      </c>
+      <c r="M46" t="n">
         <v>4.5</v>
       </c>
-      <c r="K46" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1</v>
-      </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
@@ -3590,9 +3599,6 @@
         <v>1</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
@@ -3600,7 +3606,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -3612,7 +3618,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3621,25 +3627,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J47" t="n">
         <v>4.5</v>
@@ -3650,9 +3653,6 @@
       <c r="M47" t="n">
         <v>2.5</v>
       </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
@@ -3674,8 +3674,11 @@
       <c r="V47" t="n">
         <v>1</v>
       </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
       <c r="AF47" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -3691,7 +3694,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3700,32 +3703,32 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
-      </c>
-      <c r="I48" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
         <v>4.5</v>
       </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
       <c r="S48" t="n">
         <v>1</v>
       </c>
@@ -3736,7 +3739,7 @@
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -3752,7 +3755,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3761,22 +3764,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
-      </c>
-      <c r="F49" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>4.5</v>
@@ -3787,7 +3790,7 @@
       <c r="M49" t="n">
         <v>2.5</v>
       </c>
-      <c r="O49" t="n">
+      <c r="N49" t="n">
         <v>1</v>
       </c>
       <c r="P49" t="n">
@@ -3808,11 +3811,8 @@
       <c r="V49" t="n">
         <v>1</v>
       </c>
-      <c r="Z49" t="n">
-        <v>1</v>
-      </c>
       <c r="AF49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3837,28 +3837,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
-      </c>
-      <c r="F50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
@@ -3869,15 +3860,12 @@
       <c r="T50" t="n">
         <v>1</v>
       </c>
-      <c r="V50" t="n">
-        <v>1</v>
-      </c>
       <c r="AF50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -3889,7 +3877,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3898,13 +3886,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>3</v>
@@ -3913,20 +3904,23 @@
         <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5</v>
+      </c>
+      <c r="M51" t="n">
         <v>4.5</v>
       </c>
-      <c r="K51" t="n">
-        <v>2</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N51" t="n">
         <v>1</v>
       </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
@@ -3946,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -3962,7 +3956,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Sistemas terrestres y sus interacciones</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3971,47 +3965,77 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>8</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>8</v>
       </c>
       <c r="J52" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K52" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
         <v>1</v>
       </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
       <c r="S52" t="n">
         <v>1</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
       <c r="AF52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4020,38 +4044,32 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="n">
         <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
         <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
         <v>2.5</v>
       </c>
-      <c r="K53" t="n">
-        <v>5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
@@ -4074,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4090,7 +4108,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sistemas terrestres y sus interacciones</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4099,53 +4117,35 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="n">
+        <v>7</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" t="n">
         <v>3</v>
       </c>
-      <c r="D54" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" t="n">
-        <v>8</v>
-      </c>
-      <c r="F54" t="n">
-        <v>8</v>
-      </c>
-      <c r="G54" t="n">
-        <v>6</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K54" t="n">
-        <v>2</v>
-      </c>
       <c r="M54" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
       </c>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
@@ -4153,23 +4153,23 @@
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4178,38 +4178,32 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>2.5</v>
       </c>
-      <c r="G55" t="n">
-        <v>2</v>
-      </c>
       <c r="H55" t="n">
         <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J55" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M55" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
@@ -4226,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4235,14 +4229,14 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4251,35 +4245,53 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2.5</v>
       </c>
       <c r="K56" t="n">
         <v>3</v>
       </c>
       <c r="M56" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
         <v>1</v>
       </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
@@ -4287,11 +4299,11 @@
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
@@ -4303,7 +4315,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Uso del suelo y su degradación</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4318,35 +4330,17 @@
         <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>7</v>
-      </c>
-      <c r="J57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1</v>
-      </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
@@ -4354,120 +4348,75 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
+          <t>Convección del manto y energía interna de la Tierra</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>8</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3</v>
-      </c>
-      <c r="I58" t="n">
-        <v>5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K58" t="n">
-        <v>3</v>
-      </c>
-      <c r="M58" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="n">
-        <v>1</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Uso del suelo y su degradación</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
       </c>
+      <c r="I59" t="n">
+        <v>7</v>
+      </c>
+      <c r="J59" t="n">
+        <v>7</v>
+      </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M59" t="n">
         <v>4.5</v>
@@ -4475,6 +4424,12 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
@@ -4482,72 +4437,108 @@
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
+          <t>Tectónica de placas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>incierto</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" t="n">
+        <v>8</v>
+      </c>
+      <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5</v>
+      </c>
+      <c r="J60" t="n">
+        <v>7</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>5</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Acidificación del océano</t>
+          <t>Grandes cambios globales: glaciaciones e impactos de asteroides</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
-      </c>
-      <c r="H61" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -4556,14 +4547,14 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>posterior</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Corrientes oceánicas superficiales y profundas</t>
+          <t>Acidificación del océano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4574,22 +4565,10 @@
       <c r="C62" t="n">
         <v>9</v>
       </c>
-      <c r="F62" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" t="n">
+      <c r="H62" t="n">
         <v>7</v>
       </c>
-      <c r="M62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>1</v>
-      </c>
-      <c r="V62" t="n">
+      <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="AF62" t="n">
@@ -4609,7 +4588,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mareas</t>
+          <t>Corrientes oceánicas superficiales y profundas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4618,27 +4597,18 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
-      </c>
-      <c r="D63" t="n">
-        <v>4</v>
-      </c>
-      <c r="E63" t="n">
-        <v>6</v>
-      </c>
-      <c r="H63" t="n">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8</v>
       </c>
       <c r="J63" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>7</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O63" t="n">
         <v>1</v>
       </c>
       <c r="S63" t="n">
@@ -4648,23 +4618,23 @@
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>posterior</t>
         </is>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Oleaje, dinámica costera y sedimentación marina</t>
+          <t>Mareas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4678,11 +4648,23 @@
       <c r="D64" t="n">
         <v>4</v>
       </c>
+      <c r="E64" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" t="n">
+        <v>5</v>
+      </c>
       <c r="J64" t="n">
         <v>2.5</v>
       </c>
       <c r="M64" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -4695,7 +4677,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -4707,56 +4689,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Origen del universo: el Big Bang</t>
+          <t>Oleaje, dinámica costera y sedimentación marina</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>posterior</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M65" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
           <t>sin_referente</t>
         </is>
       </c>
-      <c r="C65" t="n">
-        <v>5</v>
-      </c>
-      <c r="D65" t="n">
-        <v>5</v>
-      </c>
-      <c r="H65" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" t="n">
-        <v>7</v>
-      </c>
-      <c r="K65" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>sin_referente</t>
-        </is>
-      </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>posterior</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ciclones tropicales y tormentas</t>
+          <t>Origen del universo: el Big Bang</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4765,19 +4741,31 @@
         </is>
       </c>
       <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="H66" t="n">
         <v>4</v>
       </c>
-      <c r="D66" t="n">
-        <v>4</v>
-      </c>
-      <c r="M66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V66" t="n">
+      <c r="J66" t="n">
+        <v>7</v>
+      </c>
+      <c r="K66" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
@@ -4786,14 +4774,14 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Deriva continental y expansión del fondo oceánico</t>
+          <t>Ciclones tropicales y tormentas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4802,25 +4790,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" t="n">
-        <v>7</v>
-      </c>
-      <c r="J67" t="n">
-        <v>7</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="M67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V67" t="n">
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -4836,7 +4818,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Energía geotérmica</t>
+          <t>Deriva continental y expansión del fondo oceánico</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4845,10 +4827,25 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>7</v>
+      </c>
+      <c r="J68" t="n">
+        <v>7</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>5</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -4857,14 +4854,14 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las estrellas</t>
+          <t>Energía geotérmica</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4873,13 +4870,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -4888,14 +4882,14 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Formación y evolución temprana de la Tierra</t>
+          <t>Ciclo de vida de las estrellas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4904,16 +4898,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF70" t="n">
         <v>5</v>
@@ -4932,7 +4920,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Formación del sistema solar</t>
+          <t>Formación y evolución temprana de la Tierra</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4941,15 +4929,15 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
-      </c>
-      <c r="K71" t="n">
-        <v>8</v>
-      </c>
-      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P71" t="n">
         <v>1</v>
       </c>
       <c r="AF71" t="n">
@@ -4969,7 +4957,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Geología y geomorfología de El Salvador</t>
+          <t>Formación del sistema solar</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4978,15 +4966,15 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
-      </c>
-      <c r="F72" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O72" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" t="n">
+        <v>8</v>
+      </c>
+      <c r="T72" t="n">
         <v>1</v>
       </c>
       <c r="AF72" t="n">
@@ -5006,7 +4994,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ondas sísmicas, magnitud e intensidad</t>
+          <t>Geología y geomorfología de El Salvador</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5020,10 +5008,10 @@
       <c r="D73" t="n">
         <v>5</v>
       </c>
-      <c r="I73" t="n">
-        <v>6</v>
-      </c>
-      <c r="R73" t="n">
+      <c r="F73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
@@ -5043,7 +5031,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
+          <t>Ondas sísmicas, magnitud e intensidad</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5052,10 +5040,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
       </c>
       <c r="AF74" t="n">
         <v>5</v>
@@ -5074,7 +5068,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sismicidad de El Salvador</t>
+          <t>Precursores, monitoreo y alerta de sismos y erupciones</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5089,7 +5083,7 @@
         <v>4</v>
       </c>
       <c r="AF75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
@@ -5105,7 +5099,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tsunamis</t>
+          <t>Sismicidad de El Salvador</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5119,11 +5113,8 @@
       <c r="D76" t="n">
         <v>4</v>
       </c>
-      <c r="M76" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V76" t="n">
-        <v>1</v>
+      <c r="AF76" t="n">
+        <v>4</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -5132,14 +5123,14 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Vulcanismo de El Salvador</t>
+          <t>Tsunamis</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5153,8 +5144,11 @@
       <c r="D77" t="n">
         <v>4</v>
       </c>
-      <c r="AF77" t="n">
-        <v>4</v>
+      <c r="M77" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V77" t="n">
+        <v>1</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -5163,96 +5157,45 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Recursos naturales renovables y no renovables</t>
+          <t>Vulcanismo de El Salvador</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" t="n">
-        <v>2</v>
-      </c>
-      <c r="F78" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" t="n">
-        <v>6</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K78" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" t="n">
-        <v>5</v>
-      </c>
-      <c r="M78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1</v>
-      </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>sin_referente</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Suelo: formación, componentes y tipos</t>
+          <t>Recursos naturales renovables y no renovables</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5261,10 +5204,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -5273,19 +5216,19 @@
         <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
-      </c>
-      <c r="I79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K79" t="n">
         <v>2</v>
+      </c>
+      <c r="L79" t="n">
+        <v>5</v>
       </c>
       <c r="M79" t="n">
         <v>2.5</v>
@@ -5302,27 +5245,109 @@
       <c r="Q79" t="n">
         <v>1</v>
       </c>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
       <c r="S79" t="n">
         <v>1</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
+      <c r="U79" t="n">
+        <v>1</v>
+      </c>
       <c r="V79" t="n">
         <v>1</v>
       </c>
+      <c r="Z79" t="n">
+        <v>1</v>
+      </c>
       <c r="AF79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>adelantado</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Suelo: formación, componentes y tipos</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>tardio</t>
         </is>
       </c>
-      <c r="AH79" t="inlineStr">
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" t="n">
+        <v>7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>tardio</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
         <is>
           <t>tardio</t>
         </is>
@@ -5339,7 +5364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8670,6 +8695,48 @@
       </c>
       <c r="J79">
         <f>Datos!B79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <f>Datos!A80</f>
+        <v/>
+      </c>
+      <c r="B80">
+        <f>IF(Datos!C80="","",Datos!C80)</f>
+        <v/>
+      </c>
+      <c r="C80">
+        <f>COUNT(Datos!E80:M80)</f>
+        <v/>
+      </c>
+      <c r="D80">
+        <f>IF(C80=0,"",MEDIAN(Datos!E80:M80))</f>
+        <v/>
+      </c>
+      <c r="E80">
+        <f>COUNT(Datos!W80:AE80)</f>
+        <v/>
+      </c>
+      <c r="F80">
+        <f>IF(OR(B80="",D80=""),"",B80-D80)</f>
+        <v/>
+      </c>
+      <c r="G80">
+        <f>IF(Datos!D80="","",Datos!D80)</f>
+        <v/>
+      </c>
+      <c r="H80">
+        <f>COUNT(Datos!N80:V80)</f>
+        <v/>
+      </c>
+      <c r="I80">
+        <f>IF(B80="",IF(C80&gt;=5,"falta en SV",""),IF(G80="",IF(B80&gt;8,IF(C80&gt;=5,"SV tarde","despues del tramo"),IF(H80&gt;=5,"no retomado en 2-8","previo")),IF(B80&lt;2,"retomado",IF(AND(C80&lt;=1,E80&gt;=3),"solo especializacion",IF(F80="","coherente",IF(F80&lt;=-1.5,"SV adelantado",IF(F80&gt;=2,"SV tarde","coherente")))))))</f>
+        <v/>
+      </c>
+      <c r="J80">
+        <f>Datos!B80</f>
         <v/>
       </c>
     </row>
@@ -8709,7 +8776,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Datos!B2:B79,A2)</f>
+        <f>COUNTIF(Datos!B2:B80,A2)</f>
         <v/>
       </c>
     </row>
@@ -8720,7 +8787,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Datos!B2:B79,A3)</f>
+        <f>COUNTIF(Datos!B2:B80,A3)</f>
         <v/>
       </c>
     </row>
@@ -8731,7 +8798,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Datos!B2:B79,A4)</f>
+        <f>COUNTIF(Datos!B2:B80,A4)</f>
         <v/>
       </c>
     </row>
@@ -8742,7 +8809,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Datos!B2:B79,A5)</f>
+        <f>COUNTIF(Datos!B2:B80,A5)</f>
         <v/>
       </c>
     </row>
@@ -8753,7 +8820,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Datos!B2:B79,A6)</f>
+        <f>COUNTIF(Datos!B2:B80,A6)</f>
         <v/>
       </c>
     </row>
@@ -8764,7 +8831,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Datos!B2:B79,A7)</f>
+        <f>COUNTIF(Datos!B2:B80,A7)</f>
         <v/>
       </c>
     </row>
@@ -8775,7 +8842,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>COUNTIF(Datos!B2:B79,A8)</f>
+        <f>COUNTIF(Datos!B2:B80,A8)</f>
         <v/>
       </c>
     </row>

--- a/internacional/2_8/Contraste_tierra_espacio.xlsx
+++ b/internacional/2_8/Contraste_tierra_espacio.xlsx
@@ -1755,7 +1755,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Traslación de la Tierra y el año</t>
+          <t>Tectónica de placas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1764,35 +1764,38 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
       </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
@@ -1805,14 +1808,11 @@
       <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
       <c r="V20" t="n">
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -1821,14 +1821,14 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Volcanes: estructura, tipos y productos</t>
+          <t>Traslación de la Tierra y el año</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,21 +1837,39 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
         <v>3</v>
       </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
         <v>8</v>
       </c>
-      <c r="I21" t="n">
-        <v>5</v>
-      </c>
       <c r="J21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="R21" t="n">
@@ -1860,8 +1878,14 @@
       <c r="S21" t="n">
         <v>1</v>
       </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
       <c r="AF21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -1877,80 +1901,56 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Calentamiento global</t>
+          <t>Volcanes: estructura, tipos y productos</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
       </c>
-      <c r="G22" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3</v>
+      <c r="I22" t="n">
+        <v>5</v>
       </c>
       <c r="J22" t="n">
         <v>2.5</v>
       </c>
-      <c r="K22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>7</v>
-      </c>
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
       <c r="AF22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Calidad del aire y contaminación atmosférica</t>
+          <t>Calentamiento global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1959,19 +1959,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.5</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>7.5</v>
       </c>
       <c r="M23" t="n">
         <v>7</v>
@@ -1979,10 +1988,19 @@
       <c r="O23" t="n">
         <v>1</v>
       </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
       <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
@@ -1993,7 +2011,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -2005,7 +2023,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Campo magnético terrestre</t>
+          <t>Calidad del aire y contaminación atmosférica</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2014,77 +2032,53 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" t="n">
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="n">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cambio climático: causas y efectos</t>
+          <t>Campo magnético terrestre</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2093,32 +2087,38 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L25" t="n">
         <v>3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7.5</v>
       </c>
       <c r="M25" t="n">
         <v>4.5</v>
       </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
@@ -2128,12 +2128,12 @@
       <c r="Q25" t="n">
         <v>1</v>
       </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
       <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="AF25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -2150,14 +2150,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ciclo del agua</t>
+          <t>Cambio climático: causas y efectos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2166,41 +2166,32 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="D26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
       <c r="J26" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="M26" t="n">
         <v>4.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
@@ -2210,9 +2201,6 @@
       <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
@@ -2225,11 +2213,8 @@
       <c r="V26" t="n">
         <v>1</v>
       </c>
-      <c r="Z26" t="n">
-        <v>1</v>
-      </c>
       <c r="AF26" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -2245,7 +2230,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ciclo del carbono en los sistemas terrestres</t>
+          <t>Ciclo del agua</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2254,22 +2239,25 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>4.5</v>
@@ -2278,10 +2266,10 @@
         <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
@@ -2295,6 +2283,9 @@
       <c r="Q27" t="n">
         <v>1</v>
       </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
@@ -2307,8 +2298,11 @@
       <c r="V27" t="n">
         <v>1</v>
       </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
       <c r="AF27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -2317,14 +2311,14 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Combustibles fósiles: formación y uso</t>
+          <t>Ciclo del carbono en los sistemas terrestres</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2333,25 +2327,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4.5</v>
       </c>
       <c r="K28" t="n">
         <v>2</v>
       </c>
+      <c r="L28" t="n">
+        <v>7.5</v>
+      </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2362,17 +2368,20 @@
       <c r="Q28" t="n">
         <v>1</v>
       </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1</v>
-      </c>
       <c r="AF28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -2381,14 +2390,14 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>La atmósfera y su composición</t>
+          <t>Combustibles fósiles: formación y uso</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2397,25 +2406,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
       </c>
       <c r="G29" t="n">
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>4.5</v>
+        <v>7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2423,17 +2435,17 @@
       <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="V29" t="n">
         <v>1</v>
       </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
       <c r="AF29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2449,7 +2461,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Conservación de recursos, residuos y sostenibilidad</t>
+          <t>La atmósfera y su composición</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2458,13 +2470,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>6</v>
@@ -2472,9 +2481,6 @@
       <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="n">
-        <v>8</v>
-      </c>
       <c r="J30" t="n">
         <v>2.5</v>
       </c>
@@ -2482,10 +2488,7 @@
         <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2493,9 +2496,6 @@
       <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Abastecimiento y conservación del agua dulce</t>
+          <t>Conservación de recursos, residuos y sostenibilidad</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2531,25 +2531,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
       </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
+      <c r="I31" t="n">
+        <v>8</v>
+      </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>5</v>
       </c>
       <c r="M31" t="n">
         <v>2.5</v>
@@ -2557,30 +2560,30 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1</v>
-      </c>
       <c r="AF31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -2592,7 +2595,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cuencas hidrográficas y aguas superficiales</t>
+          <t>Abastecimiento y conservación del agua dulce</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2601,45 +2604,48 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M32" t="n">
         <v>2.5</v>
       </c>
-      <c r="H32" t="n">
-        <v>7</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
       <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
@@ -2659,7 +2665,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Efecto invernadero</t>
+          <t>Cuencas hidrográficas y aguas superficiales</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2668,53 +2674,53 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
         <v>7</v>
       </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K33" t="n">
-        <v>5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>7</v>
-      </c>
-      <c r="P33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
       <c r="S33" t="n">
         <v>1</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -2726,7 +2732,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación</t>
+          <t>Efecto invernadero</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2735,40 +2741,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>7.5</v>
       </c>
       <c r="M34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -2776,20 +2770,20 @@
       <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -2805,7 +2799,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estrellas y nebulosas</t>
+          <t>Erosión, transporte y sedimentación</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2818,23 +2812,41 @@
       </c>
       <c r="D35" t="n">
         <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>6</v>
       </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
       </c>
       <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="R35" t="n">
@@ -2866,7 +2878,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Exploración espacial</t>
+          <t>Estrellas y nebulosas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2875,24 +2887,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="n">
         <v>3</v>
       </c>
-      <c r="I36" t="n">
-        <v>4</v>
-      </c>
       <c r="J36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
         <v>7</v>
       </c>
-      <c r="K36" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q36" t="n">
+      <c r="P36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
@@ -2904,8 +2919,11 @@
       <c r="T36" t="n">
         <v>1</v>
       </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
       <c r="AF36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -2921,7 +2939,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fases de la Luna</t>
+          <t>Exploración espacial</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2935,32 +2953,17 @@
       <c r="D37" t="n">
         <v>4</v>
       </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>2</v>
-      </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
-      </c>
-      <c r="M37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
@@ -2972,9 +2975,6 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
         <v>1</v>
       </c>
       <c r="AF37" t="n">
@@ -2994,7 +2994,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gravedad y órbitas</t>
+          <t>Fases de la Luna</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3003,10 +3003,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>3</v>
@@ -3015,13 +3018,19 @@
         <v>2</v>
       </c>
       <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" t="n">
-        <v>7</v>
-      </c>
       <c r="M38" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3033,6 +3042,9 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="V38" t="n">
@@ -3055,7 +3067,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hidrosfera: distribución del agua dulce y salada</t>
+          <t>Gravedad y órbitas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3069,44 +3081,38 @@
       <c r="D39" t="n">
         <v>3</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>5</v>
-      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
+      <c r="I39" t="n">
+        <v>8</v>
+      </c>
       <c r="J39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
         <v>4.5</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3122,7 +3128,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
+          <t>Hidrosfera: distribución del agua dulce y salada</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3131,50 +3137,38 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" t="n">
         <v>2.5</v>
       </c>
-      <c r="G40" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" t="n">
-        <v>8</v>
-      </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
         <v>4.5</v>
       </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N40" t="n">
         <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
@@ -3185,11 +3179,11 @@
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -3201,7 +3195,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>La Luna: características y origen</t>
+          <t>Inclinación del eje terrestre y estaciones astronómicas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3210,25 +3204,40 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.5</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
         <v>2.5</v>
       </c>
-      <c r="M41" t="n">
-        <v>7</v>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3242,15 +3251,18 @@
       <c r="S41" t="n">
         <v>1</v>
       </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
       <c r="V41" t="n">
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -3262,7 +3274,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Meteorización</t>
+          <t>Interacción océano-atmósfera</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3271,41 +3283,29 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
-      </c>
-      <c r="E42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
       </c>
-      <c r="G42" t="n">
-        <v>2</v>
-      </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J42" t="n">
         <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
       <c r="R42" t="n">
         <v>1</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3328,14 +3328,14 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Minerales y sus propiedades</t>
+          <t>La Luna: características y origen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3344,49 +3344,43 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" t="n">
-        <v>7</v>
-      </c>
-      <c r="K43" t="n">
-        <v>3</v>
-      </c>
-      <c r="M43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
       <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
       </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -3402,7 +3396,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Formación de nubes y precipitación</t>
+          <t>Meteorización</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3411,25 +3405,25 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
         <v>4</v>
       </c>
-      <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3</v>
-      </c>
       <c r="F44" t="n">
         <v>5</v>
       </c>
-      <c r="H44" t="n">
+      <c r="G44" t="n">
         <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
       <c r="J44" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
         <v>2</v>
@@ -3443,7 +3437,7 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="R44" t="n">
@@ -3458,11 +3452,8 @@
       <c r="V44" t="n">
         <v>1</v>
       </c>
-      <c r="Z44" t="n">
-        <v>1</v>
-      </c>
       <c r="AF44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3478,7 +3469,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Patrones estacionales: época seca y lluviosa</t>
+          <t>Minerales y sus propiedades</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3487,50 +3478,38 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
-      <c r="F45" t="n">
-        <v>2.5</v>
-      </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="J45" t="n">
+      <c r="M45" t="n">
         <v>4.5</v>
       </c>
-      <c r="K45" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.5</v>
-      </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
       <c r="S45" t="n">
         <v>1</v>
       </c>
@@ -3541,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -3557,7 +3536,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Planetas: tipos y comparación</t>
+          <t>Formación de nubes y precipitación</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3571,20 +3550,32 @@
       <c r="D46" t="n">
         <v>4</v>
       </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5</v>
+      </c>
       <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
         <v>4</v>
       </c>
-      <c r="I46" t="n">
-        <v>8</v>
-      </c>
       <c r="J46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K46" t="n">
-        <v>5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>4.5</v>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
@@ -3599,6 +3590,9 @@
         <v>1</v>
       </c>
       <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
         <v>1</v>
       </c>
       <c r="AF46" t="n">
@@ -3606,7 +3600,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
@@ -3618,7 +3612,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
+          <t>Patrones estacionales: época seca y lluviosa</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3627,22 +3621,25 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G47" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>4.5</v>
@@ -3653,6 +3650,9 @@
       <c r="M47" t="n">
         <v>2.5</v>
       </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
@@ -3674,11 +3674,8 @@
       <c r="V47" t="n">
         <v>1</v>
       </c>
-      <c r="Z47" t="n">
-        <v>1</v>
-      </c>
       <c r="AF47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -3694,7 +3691,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Recursos minerales y minería</t>
+          <t>Planetas: tipos y comparación</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3703,32 +3700,32 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8</v>
       </c>
       <c r="J48" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
         <v>4.5</v>
       </c>
-      <c r="O48" t="n">
-        <v>1</v>
-      </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
       <c r="S48" t="n">
         <v>1</v>
       </c>
@@ -3739,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -3755,7 +3752,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rotación de la Tierra: día, noche y sombras</t>
+          <t>Calentamiento desigual de la Tierra y circulación atmosférica</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3764,22 +3761,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
         <v>4.5</v>
@@ -3790,7 +3787,7 @@
       <c r="M49" t="n">
         <v>2.5</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>1</v>
       </c>
       <c r="P49" t="n">
@@ -3811,8 +3808,11 @@
       <c r="V49" t="n">
         <v>1</v>
       </c>
+      <c r="Z49" t="n">
+        <v>1</v>
+      </c>
       <c r="AF49" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Satélites, asteroides y cometas</t>
+          <t>Recursos minerales y minería</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3837,19 +3837,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
       </c>
       <c r="H50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
         <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
@@ -3860,12 +3869,15 @@
       <c r="T50" t="n">
         <v>1</v>
       </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
       <c r="AF50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -3877,7 +3889,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>El sistema solar y el modelo heliocéntrico</t>
+          <t>Rotación de la Tierra: día, noche y sombras</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3886,16 +3898,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
-      </c>
-      <c r="F51" t="n">
-        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>3</v>
@@ -3904,23 +3913,20 @@
         <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2</v>
+      </c>
+      <c r="M51" t="n">
         <v>2.5</v>
       </c>
-      <c r="K51" t="n">
-        <v>5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4.5</v>
-      </c>
       <c r="N51" t="n">
         <v>1</v>
       </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
@@ -3940,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -3956,7 +3962,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sistemas terrestres y sus interacciones</t>
+          <t>Satélites, asteroides y cometas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3965,77 +3971,47 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" t="n">
-        <v>8</v>
-      </c>
-      <c r="F52" t="n">
-        <v>8</v>
-      </c>
-      <c r="G52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q52" t="n">
         <v>1</v>
       </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
       <c r="S52" t="n">
         <v>1</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
-      <c r="V52" t="n">
-        <v>1</v>
-      </c>
       <c r="AF52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>El sistema solar y el modelo heliocéntrico</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4044,31 +4020,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="n">
         <v>2</v>
       </c>
       <c r="F53" t="n">
+        <v>5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" t="n">
         <v>2.5</v>
       </c>
-      <c r="G53" t="n">
-        <v>2</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
+        <v>5</v>
+      </c>
+      <c r="M53" t="n">
         <v>4.5</v>
       </c>
-      <c r="K53" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" t="n">
-        <v>2.5</v>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -4092,7 +4074,7 @@
         <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -4108,7 +4090,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tiempo geológico y datación</t>
+          <t>Sistemas terrestres y sus interacciones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4117,35 +4099,53 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F54" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6</v>
       </c>
       <c r="H54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.5</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="N54" t="n">
         <v>1</v>
       </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
       </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
@@ -4153,23 +4153,23 @@
         <v>1</v>
       </c>
       <c r="AF54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>adelantado</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Clima: diferencia con el tiempo, tipos y factores</t>
+          <t>Tiempo atmosférico y sus variables</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4178,32 +4178,38 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>2.5</v>
       </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
       <c r="H55" t="n">
         <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
@@ -4220,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -4229,14 +4235,14 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
+          <t>Tiempo geológico y datación</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4245,53 +4251,35 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" t="n">
-        <v>8</v>
-      </c>
-      <c r="G56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="K56" t="n">
         <v>3</v>
       </c>
       <c r="M56" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N56" t="n">
         <v>1</v>
       </c>
-      <c r="O56" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="R56" t="n">
         <v>1</v>
       </c>
-      <c r="S56" t="n">
-        <v>1</v>
-      </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
@@ -4299,11 +4287,11 @@
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
@@ -4315,7 +4303,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Uso del suelo y su degradación</t>
+          <t>Clima: diferencia con el tiempo, tipos y factores</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4330,17 +4318,35 @@
         <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>2.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
       </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
@@ -4348,75 +4354,120 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>adelantado</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Convección del manto y energía interna de la Tierra</t>
+          <t>Tipos de rocas: ígneas, sedimentarias y metamórficas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>3</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Interacción océano-atmósfera</t>
+          <t>Uso del suelo y su degradación</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>alineado</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
       </c>
-      <c r="I59" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7</v>
-      </c>
       <c r="K59" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
         <v>4.5</v>
@@ -4424,12 +4475,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
-      <c r="S59" t="n">
-        <v>1</v>
-      </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
@@ -4437,89 +4482,44 @@
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tectónica de placas</t>
+          <t>Convección del manto y energía interna de la Tierra</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" t="n">
         <v>7</v>
       </c>
-      <c r="F60" t="n">
-        <v>8</v>
-      </c>
-      <c r="G60" t="n">
-        <v>6</v>
-      </c>
-      <c r="H60" t="n">
-        <v>4</v>
-      </c>
-      <c r="I60" t="n">
-        <v>5</v>
-      </c>
-      <c r="J60" t="n">
-        <v>7</v>
-      </c>
-      <c r="M60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
-      <c r="S60" t="n">
-        <v>1</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>5</v>
-      </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>adelantado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
